--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -2609,7 +2609,8 @@
 siyaṃsu</t>
   </si>
   <si>
-    <t xml:space="preserve">dvīsu
+    <t xml:space="preserve">dvisu
+dvīsu
 duvesu</t>
   </si>
   <si>

--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -7095,12 +7095,10 @@
     <t xml:space="preserve">kubbamhe</t>
   </si>
   <si>
-    <t xml:space="preserve">karotu
-kubbatu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">karontu
-kubbantu</t>
+    <t xml:space="preserve">kubbatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubbantu</t>
   </si>
   <si>
     <t xml:space="preserve">kubbataṃ</t>
@@ -7126,8 +7124,7 @@
 kubbaye</t>
   </si>
   <si>
-    <t xml:space="preserve">kareyyuṃ
-kubbeyyuṃ
+    <t xml:space="preserve">kubbeyyuṃ
 kayiruṃ</t>
   </si>
   <si>
@@ -7202,7 +7199,9 @@
     <t xml:space="preserve">karaṃ</t>
   </si>
   <si>
-    <t xml:space="preserve">karimhe</t>
+    <t xml:space="preserve">karimhe
+karamhasa
+karamhase</t>
   </si>
   <si>
     <t xml:space="preserve">jantu</t>
@@ -66151,7 +66150,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="41.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="21" t="s">
         <v>482</v>
       </c>

--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9967" uniqueCount="2678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9962" uniqueCount="2678">
   <si>
     <t xml:space="preserve">inflection name</t>
   </si>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">i2 card</t>
   </si>
   <si>
-    <t xml:space="preserve">O83:S92</t>
+    <t xml:space="preserve">O83:S91</t>
   </si>
   <si>
     <t xml:space="preserve">koṭi</t>
@@ -1759,7 +1759,8 @@
 ekasmā</t>
   </si>
   <si>
-    <t xml:space="preserve">mayā</t>
+    <t xml:space="preserve">mayā
+mamato</t>
   </si>
   <si>
     <t xml:space="preserve">1st abl sg</t>
@@ -3097,6 +3098,10 @@
   <si>
     <t xml:space="preserve">imhi
 ismiṃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i
+e</t>
   </si>
   <si>
     <t xml:space="preserve">caturo
@@ -3888,7 +3893,8 @@
   </si>
   <si>
     <t xml:space="preserve">ārānaṃ
-ānaṃ</t>
+ānaṃ
+ūnaṃ</t>
   </si>
   <si>
     <t xml:space="preserve">āya
@@ -4231,11 +4237,6 @@
   </si>
   <si>
     <t xml:space="preserve">nadīnaṃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unā
-umhā
-usmā</t>
   </si>
   <si>
     <t xml:space="preserve">ūhi
@@ -5371,7 +5372,8 @@
   </si>
   <si>
     <t xml:space="preserve">raññā
-rājena</t>
+rājena
+rājinā</t>
   </si>
   <si>
     <t xml:space="preserve">rājubhi
@@ -6395,7 +6397,6 @@
   </si>
   <si>
     <t xml:space="preserve">mātarā
-mātu
 mātuyā
 matyā</t>
   </si>
@@ -6443,11 +6444,6 @@
     <t xml:space="preserve">arahatā
 arahantamhā
 arahantasmā</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mātarā
-mātuyā
-matyā</t>
   </si>
   <si>
     <t xml:space="preserve">arahato
@@ -7202,6 +7198,11 @@
     <t xml:space="preserve">karimhe
 karamhasa
 karamhase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unā
+umhā
+usmā</t>
   </si>
   <si>
     <t xml:space="preserve">jantu</t>
@@ -42485,7 +42486,7 @@
       <c r="CN32" s="22"/>
       <c r="CP32" s="22"/>
     </row>
-    <row r="33" customFormat="false" ht="28.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="28.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="48"/>
@@ -42575,7 +42576,7 @@
         <v>627</v>
       </c>
       <c r="BF33" s="41" t="s">
-        <v>720</v>
+        <v>927</v>
       </c>
       <c r="BG33" s="56" t="s">
         <v>629</v>
@@ -42673,7 +42674,7 @@
       </c>
       <c r="DA33" s="47"/>
     </row>
-    <row r="34" customFormat="false" ht="28.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="27.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21"/>
       <c r="B34" s="21"/>
       <c r="C34" s="48"/>
@@ -42691,19 +42692,19 @@
         <v>417</v>
       </c>
       <c r="P34" s="23" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="Q34" s="50" t="s">
         <v>421</v>
       </c>
       <c r="R34" s="38" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="S34" s="51" t="s">
         <v>425</v>
       </c>
       <c r="T34" s="23" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="U34" s="50" t="s">
         <v>429</v>
@@ -42715,37 +42716,37 @@
         <v>417</v>
       </c>
       <c r="AD34" s="24" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AE34" s="53" t="s">
         <v>419</v>
       </c>
       <c r="AF34" s="24" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AG34" s="53" t="s">
         <v>421</v>
       </c>
       <c r="AH34" s="67" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AI34" s="69" t="s">
         <v>423</v>
       </c>
       <c r="AJ34" s="67" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AK34" s="69" t="s">
         <v>425</v>
       </c>
       <c r="AL34" s="24" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AM34" s="53" t="s">
         <v>427</v>
       </c>
       <c r="AN34" s="24" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="AO34" s="53" t="s">
         <v>429</v>
@@ -42754,25 +42755,25 @@
         <v>417</v>
       </c>
       <c r="AR34" s="25" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AS34" s="54" t="s">
         <v>419</v>
       </c>
       <c r="AT34" s="25" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AU34" s="54" t="s">
         <v>421</v>
       </c>
       <c r="AV34" s="40" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AW34" s="55" t="s">
         <v>423</v>
       </c>
       <c r="AX34" s="40" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AY34" s="55" t="s">
         <v>425</v>
@@ -42784,7 +42785,7 @@
         <v>427</v>
       </c>
       <c r="BB34" s="25" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="BC34" s="54" t="s">
         <v>429</v>
@@ -42826,7 +42827,7 @@
         <v>443</v>
       </c>
       <c r="CJ34" s="59" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="CK34" s="60" t="s">
         <v>445</v>
@@ -42838,7 +42839,7 @@
         <v>447</v>
       </c>
       <c r="CN34" s="59" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="CO34" s="60" t="s">
         <v>449</v>
@@ -42853,28 +42854,28 @@
         <v>673</v>
       </c>
       <c r="CT34" s="70" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="CU34" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV34" s="70" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="CW34" s="71" t="s">
         <v>677</v>
       </c>
       <c r="CX34" s="70" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="CY34" s="71" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CZ34" s="70" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="DA34" s="71" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42882,19 +42883,19 @@
         <v>455</v>
       </c>
       <c r="P35" s="23" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="Q35" s="50" t="s">
         <v>458</v>
       </c>
       <c r="R35" s="38" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="S35" s="51" t="s">
         <v>460</v>
       </c>
       <c r="T35" s="23" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="U35" s="50" t="s">
         <v>463</v>
@@ -42906,37 +42907,37 @@
         <v>455</v>
       </c>
       <c r="AD35" s="24" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AE35" s="53" t="s">
         <v>456</v>
       </c>
       <c r="AF35" s="24" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AG35" s="53" t="s">
         <v>458</v>
       </c>
       <c r="AH35" s="67" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AI35" s="69" t="s">
         <v>459</v>
       </c>
       <c r="AJ35" s="67" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AK35" s="69" t="s">
         <v>460</v>
       </c>
       <c r="AL35" s="24" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AM35" s="53" t="s">
         <v>461</v>
       </c>
       <c r="AN35" s="24" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="AO35" s="53" t="s">
         <v>463</v>
@@ -42945,37 +42946,37 @@
         <v>455</v>
       </c>
       <c r="AR35" s="25" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AS35" s="54" t="s">
         <v>456</v>
       </c>
       <c r="AT35" s="25" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AU35" s="54" t="s">
         <v>458</v>
       </c>
       <c r="AV35" s="40" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="AW35" s="55" t="s">
         <v>459</v>
       </c>
       <c r="AX35" s="40" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AY35" s="55" t="s">
         <v>460</v>
       </c>
       <c r="AZ35" s="25" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="BA35" s="54" t="s">
         <v>461</v>
       </c>
       <c r="BB35" s="25" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="BC35" s="54" t="s">
         <v>463</v>
@@ -42993,19 +42994,19 @@
         <v>470</v>
       </c>
       <c r="CJ35" s="59" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="CK35" s="60" t="s">
         <v>472</v>
       </c>
       <c r="CL35" s="59" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="CM35" s="60" t="s">
         <v>474</v>
       </c>
       <c r="CN35" s="59" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="CO35" s="60" t="s">
         <v>476</v>
@@ -43020,28 +43021,28 @@
         <v>700</v>
       </c>
       <c r="CT35" s="70" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="CU35" s="71" t="s">
         <v>701</v>
       </c>
       <c r="CV35" s="70" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="CW35" s="71" t="s">
         <v>703</v>
       </c>
       <c r="CX35" s="70" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="CY35" s="71" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CZ35" s="70" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="DA35" s="71" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="68.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43076,19 +43077,19 @@
         <v>482</v>
       </c>
       <c r="P36" s="23" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Q36" s="50" t="s">
         <v>486</v>
       </c>
       <c r="R36" s="38" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="S36" s="51" t="s">
         <v>490</v>
       </c>
       <c r="T36" s="23" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="U36" s="50" t="s">
         <v>492</v>
@@ -43100,37 +43101,37 @@
         <v>482</v>
       </c>
       <c r="AD36" s="24" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AE36" s="53" t="s">
         <v>484</v>
       </c>
       <c r="AF36" s="24" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AG36" s="53" t="s">
         <v>486</v>
       </c>
       <c r="AH36" s="67" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AI36" s="69" t="s">
         <v>488</v>
       </c>
       <c r="AJ36" s="67" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AK36" s="69" t="s">
         <v>490</v>
       </c>
       <c r="AL36" s="24" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AM36" s="53" t="s">
         <v>491</v>
       </c>
       <c r="AN36" s="24" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AO36" s="53" t="s">
         <v>492</v>
@@ -43139,37 +43140,37 @@
         <v>482</v>
       </c>
       <c r="AR36" s="25" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AS36" s="54" t="s">
         <v>484</v>
       </c>
       <c r="AT36" s="25" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AU36" s="54" t="s">
         <v>486</v>
       </c>
       <c r="AV36" s="40" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AW36" s="55" t="s">
         <v>488</v>
       </c>
       <c r="AX36" s="40" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AY36" s="55" t="s">
         <v>490</v>
       </c>
       <c r="AZ36" s="25" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="BA36" s="54" t="s">
         <v>491</v>
       </c>
       <c r="BB36" s="25" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="BC36" s="54" t="s">
         <v>492</v>
@@ -43252,28 +43253,28 @@
         <v>733</v>
       </c>
       <c r="CT36" s="70" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="CU36" s="71" t="s">
         <v>735</v>
       </c>
       <c r="CV36" s="70" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="CW36" s="71" t="s">
         <v>737</v>
       </c>
       <c r="CX36" s="70" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="CY36" s="71" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CZ36" s="70" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="DA36" s="71" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="69.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43281,37 +43282,37 @@
         <v>417</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>419</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E37" s="48" t="s">
         <v>421</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G37" s="49" t="s">
         <v>423</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I37" s="49" t="s">
         <v>425</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K37" s="48" t="s">
         <v>427</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M37" s="48" t="s">
         <v>429</v>
@@ -43320,19 +43321,19 @@
         <v>519</v>
       </c>
       <c r="P37" s="23" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="Q37" s="50" t="s">
         <v>523</v>
       </c>
       <c r="R37" s="38" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="S37" s="51" t="s">
         <v>526</v>
       </c>
       <c r="T37" s="23" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="U37" s="50" t="s">
         <v>528</v>
@@ -43344,37 +43345,37 @@
         <v>519</v>
       </c>
       <c r="AD37" s="24" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AE37" s="53" t="s">
         <v>521</v>
       </c>
       <c r="AF37" s="24" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AG37" s="53" t="s">
         <v>523</v>
       </c>
       <c r="AH37" s="67" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="AI37" s="69" t="s">
         <v>524</v>
       </c>
       <c r="AJ37" s="67" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AK37" s="69" t="s">
         <v>526</v>
       </c>
       <c r="AL37" s="24" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AM37" s="53" t="s">
         <v>527</v>
       </c>
       <c r="AN37" s="24" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AO37" s="53" t="s">
         <v>528</v>
@@ -43383,37 +43384,37 @@
         <v>519</v>
       </c>
       <c r="AR37" s="25" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AS37" s="54" t="s">
         <v>521</v>
       </c>
       <c r="AT37" s="25" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="AU37" s="54" t="s">
         <v>523</v>
       </c>
       <c r="AV37" s="40" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AW37" s="55" t="s">
         <v>524</v>
       </c>
       <c r="AX37" s="40" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="AY37" s="55" t="s">
         <v>526</v>
       </c>
       <c r="AZ37" s="25" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="BA37" s="54" t="s">
         <v>527</v>
       </c>
       <c r="BB37" s="25" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="BC37" s="54" t="s">
         <v>528</v>
@@ -43428,7 +43429,7 @@
         <v>419</v>
       </c>
       <c r="BH37" s="41" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="BI37" s="56" t="s">
         <v>421</v>
@@ -43437,7 +43438,7 @@
         <v>417</v>
       </c>
       <c r="BL37" s="41" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="BM37" s="56" t="s">
         <v>421</v>
@@ -43452,7 +43453,7 @@
         <v>423</v>
       </c>
       <c r="BT37" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BU37" s="57" t="s">
         <v>425</v>
@@ -43461,7 +43462,7 @@
         <v>423</v>
       </c>
       <c r="BX37" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BY37" s="57" t="s">
         <v>425</v>
@@ -43470,13 +43471,13 @@
         <v>417</v>
       </c>
       <c r="CD37" s="28" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="CE37" s="58" t="s">
         <v>427</v>
       </c>
       <c r="CF37" s="28" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="CG37" s="58" t="s">
         <v>429</v>
@@ -43485,7 +43486,7 @@
         <v>538</v>
       </c>
       <c r="CJ37" s="29" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="CK37" s="64" t="s">
         <v>540</v>
@@ -43544,13 +43545,13 @@
         <v>458</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="G38" s="49" t="s">
         <v>459</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="I38" s="49" t="s">
         <v>460</v>
@@ -43562,7 +43563,7 @@
         <v>461</v>
       </c>
       <c r="L38" s="21" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M38" s="48" t="s">
         <v>463</v>
@@ -43571,19 +43572,19 @@
         <v>549</v>
       </c>
       <c r="P38" s="23" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="Q38" s="50" t="s">
         <v>552</v>
       </c>
       <c r="R38" s="38" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="S38" s="51" t="s">
         <v>554</v>
       </c>
       <c r="T38" s="23" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="U38" s="50" t="s">
         <v>557</v>
@@ -43595,37 +43596,37 @@
         <v>549</v>
       </c>
       <c r="AD38" s="24" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AE38" s="53" t="s">
         <v>551</v>
       </c>
       <c r="AF38" s="24" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AG38" s="53" t="s">
         <v>552</v>
       </c>
       <c r="AH38" s="67" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AI38" s="69" t="s">
         <v>553</v>
       </c>
       <c r="AJ38" s="67" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AK38" s="69" t="s">
         <v>554</v>
       </c>
       <c r="AL38" s="24" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AM38" s="53" t="s">
         <v>556</v>
       </c>
       <c r="AN38" s="24" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AO38" s="53" t="s">
         <v>557</v>
@@ -43634,37 +43635,37 @@
         <v>549</v>
       </c>
       <c r="AR38" s="25" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="AS38" s="54" t="s">
         <v>551</v>
       </c>
       <c r="AT38" s="25" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AU38" s="54" t="s">
         <v>552</v>
       </c>
       <c r="AV38" s="40" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AW38" s="55" t="s">
         <v>553</v>
       </c>
       <c r="AX38" s="40" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AY38" s="55" t="s">
         <v>554</v>
       </c>
       <c r="AZ38" s="25" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="BA38" s="54" t="s">
         <v>556</v>
       </c>
       <c r="BB38" s="25" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="BC38" s="54" t="s">
         <v>557</v>
@@ -43673,13 +43674,13 @@
         <v>455</v>
       </c>
       <c r="BF38" s="41" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="BG38" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH38" s="41" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="BI38" s="56" t="s">
         <v>458</v>
@@ -43688,7 +43689,7 @@
         <v>455</v>
       </c>
       <c r="BL38" s="41" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="BM38" s="56" t="s">
         <v>458</v>
@@ -43703,7 +43704,7 @@
         <v>459</v>
       </c>
       <c r="BT38" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BU38" s="57" t="s">
         <v>460</v>
@@ -43712,7 +43713,7 @@
         <v>459</v>
       </c>
       <c r="BX38" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BY38" s="57" t="s">
         <v>460</v>
@@ -43721,13 +43722,13 @@
         <v>455</v>
       </c>
       <c r="CD38" s="28" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="CE38" s="58" t="s">
         <v>461</v>
       </c>
       <c r="CF38" s="28" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="CG38" s="58" t="s">
         <v>463</v>
@@ -43736,13 +43737,13 @@
         <v>567</v>
       </c>
       <c r="CJ38" s="29" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="CK38" s="64" t="s">
         <v>569</v>
       </c>
       <c r="CL38" s="29" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="CM38" s="64" t="s">
         <v>570</v>
@@ -43777,13 +43778,13 @@
         <v>486</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G39" s="49" t="s">
         <v>488</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="I39" s="49" t="s">
         <v>490</v>
@@ -43804,19 +43805,19 @@
         <v>576</v>
       </c>
       <c r="P39" s="23" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="Q39" s="50" t="s">
         <v>579</v>
       </c>
       <c r="R39" s="38" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="S39" s="51" t="s">
         <v>581</v>
       </c>
       <c r="T39" s="23" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="U39" s="50" t="s">
         <v>583</v>
@@ -43828,37 +43829,37 @@
         <v>576</v>
       </c>
       <c r="AD39" s="24" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AE39" s="53" t="s">
         <v>578</v>
       </c>
       <c r="AF39" s="24" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AG39" s="53" t="s">
         <v>579</v>
       </c>
       <c r="AH39" s="67" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="AI39" s="69" t="s">
         <v>580</v>
       </c>
       <c r="AJ39" s="67" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AK39" s="69" t="s">
         <v>581</v>
       </c>
       <c r="AL39" s="24" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AM39" s="53" t="s">
         <v>582</v>
       </c>
       <c r="AN39" s="24" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AO39" s="53" t="s">
         <v>583</v>
@@ -43867,37 +43868,37 @@
         <v>576</v>
       </c>
       <c r="AR39" s="25" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AS39" s="54" t="s">
         <v>578</v>
       </c>
       <c r="AT39" s="25" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="AU39" s="54" t="s">
         <v>579</v>
       </c>
       <c r="AV39" s="40" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AW39" s="55" t="s">
         <v>580</v>
       </c>
       <c r="AX39" s="40" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="AY39" s="55" t="s">
         <v>581</v>
       </c>
       <c r="AZ39" s="25" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="BA39" s="54" t="s">
         <v>582</v>
       </c>
       <c r="BB39" s="25" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="BC39" s="54" t="s">
         <v>583</v>
@@ -43906,7 +43907,7 @@
         <v>482</v>
       </c>
       <c r="BF39" s="41" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="BG39" s="56" t="s">
         <v>484</v>
@@ -43930,7 +43931,7 @@
         <v>482</v>
       </c>
       <c r="BR39" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS39" s="57" t="s">
         <v>488</v>
@@ -43954,13 +43955,13 @@
         <v>482</v>
       </c>
       <c r="CD39" s="28" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="CE39" s="58" t="s">
         <v>491</v>
       </c>
       <c r="CF39" s="28" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="CG39" s="58" t="s">
         <v>492</v>
@@ -44038,13 +44039,13 @@
         <v>523</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G40" s="49" t="s">
         <v>524</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I40" s="49" t="s">
         <v>526</v>
@@ -44065,19 +44066,19 @@
         <v>596</v>
       </c>
       <c r="P40" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="Q40" s="50" t="s">
         <v>600</v>
       </c>
       <c r="R40" s="38" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="S40" s="51" t="s">
         <v>604</v>
       </c>
       <c r="T40" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="U40" s="50" t="s">
         <v>606</v>
@@ -44089,37 +44090,37 @@
         <v>596</v>
       </c>
       <c r="AD40" s="24" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AE40" s="53" t="s">
         <v>598</v>
       </c>
       <c r="AF40" s="24" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AG40" s="53" t="s">
         <v>600</v>
       </c>
       <c r="AH40" s="67" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AI40" s="69" t="s">
         <v>602</v>
       </c>
       <c r="AJ40" s="67" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AK40" s="69" t="s">
         <v>604</v>
       </c>
       <c r="AL40" s="24" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AM40" s="53" t="s">
         <v>605</v>
       </c>
       <c r="AN40" s="24" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AO40" s="53" t="s">
         <v>606</v>
@@ -44128,37 +44129,37 @@
         <v>596</v>
       </c>
       <c r="AR40" s="25" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="AS40" s="54" t="s">
         <v>598</v>
       </c>
       <c r="AT40" s="25" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AU40" s="54" t="s">
         <v>600</v>
       </c>
       <c r="AV40" s="40" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AW40" s="55" t="s">
         <v>602</v>
       </c>
       <c r="AX40" s="40" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AY40" s="55" t="s">
         <v>604</v>
       </c>
       <c r="AZ40" s="25" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="BA40" s="54" t="s">
         <v>605</v>
       </c>
       <c r="BB40" s="25" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="BC40" s="54" t="s">
         <v>606</v>
@@ -44173,7 +44174,7 @@
         <v>521</v>
       </c>
       <c r="BH40" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BI40" s="56" t="s">
         <v>523</v>
@@ -44182,7 +44183,7 @@
         <v>519</v>
       </c>
       <c r="BL40" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BM40" s="56" t="s">
         <v>523</v>
@@ -44191,7 +44192,7 @@
         <v>519</v>
       </c>
       <c r="BR40" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS40" s="57" t="s">
         <v>524</v>
@@ -44215,13 +44216,13 @@
         <v>519</v>
       </c>
       <c r="CD40" s="28" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="CE40" s="58" t="s">
         <v>527</v>
       </c>
       <c r="CF40" s="28" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="CG40" s="58" t="s">
         <v>528</v>
@@ -44266,25 +44267,25 @@
         <v>443</v>
       </c>
       <c r="DD40" s="70" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="DE40" s="71" t="s">
         <v>445</v>
       </c>
       <c r="DF40" s="70" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="DG40" s="71" t="s">
         <v>447</v>
       </c>
       <c r="DH40" s="70" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="DI40" s="71" t="s">
         <v>449</v>
       </c>
       <c r="DJ40" s="70" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="DK40" s="71" t="s">
         <v>451</v>
@@ -44295,7 +44296,7 @@
         <v>549</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C41" s="48" t="s">
         <v>551</v>
@@ -44307,19 +44308,19 @@
         <v>552</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G41" s="49" t="s">
         <v>553</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="I41" s="49" t="s">
         <v>554</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="K41" s="48" t="s">
         <v>556</v>
@@ -44334,7 +44335,7 @@
         <v>636</v>
       </c>
       <c r="P41" s="23" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="Q41" s="50" t="s">
         <v>636</v>
@@ -44350,7 +44351,7 @@
         <v>636</v>
       </c>
       <c r="AD41" s="24" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AE41" s="53" t="s">
         <v>636</v>
@@ -44369,37 +44370,37 @@
         <v>627</v>
       </c>
       <c r="AR41" s="25" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AS41" s="54" t="s">
         <v>629</v>
       </c>
       <c r="AT41" s="25" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AU41" s="54" t="s">
         <v>630</v>
       </c>
       <c r="AV41" s="40" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AW41" s="55" t="s">
         <v>631</v>
       </c>
       <c r="AX41" s="40" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AY41" s="55" t="s">
         <v>632</v>
       </c>
       <c r="AZ41" s="25" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="BA41" s="54" t="s">
         <v>633</v>
       </c>
       <c r="BB41" s="25" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="BC41" s="54" t="s">
         <v>635</v>
@@ -44408,7 +44409,7 @@
         <v>549</v>
       </c>
       <c r="BF41" s="41" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="BG41" s="56" t="s">
         <v>551</v>
@@ -44432,7 +44433,7 @@
         <v>549</v>
       </c>
       <c r="BR41" s="27" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="BS41" s="57" t="s">
         <v>553</v>
@@ -44456,13 +44457,13 @@
         <v>549</v>
       </c>
       <c r="CD41" s="28" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="CE41" s="58" t="s">
         <v>556</v>
       </c>
       <c r="CF41" s="28" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="CG41" s="58" t="s">
         <v>557</v>
@@ -44483,7 +44484,7 @@
         <v>646</v>
       </c>
       <c r="CN41" s="59" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="CO41" s="60" t="s">
         <v>648</v>
@@ -44507,25 +44508,25 @@
         <v>470</v>
       </c>
       <c r="DD41" s="70" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="DE41" s="71" t="s">
         <v>472</v>
       </c>
       <c r="DF41" s="70" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="DG41" s="71" t="s">
         <v>474</v>
       </c>
       <c r="DH41" s="70" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="DI41" s="71" t="s">
         <v>476</v>
       </c>
       <c r="DJ41" s="70" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="DK41" s="71" t="s">
         <v>478</v>
@@ -44548,13 +44549,13 @@
         <v>579</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G42" s="49" t="s">
         <v>580</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I42" s="49" t="s">
         <v>581</v>
@@ -44601,7 +44602,7 @@
         <v>578</v>
       </c>
       <c r="BH42" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BI42" s="56" t="s">
         <v>579</v>
@@ -44610,7 +44611,7 @@
         <v>576</v>
       </c>
       <c r="BL42" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BM42" s="56" t="s">
         <v>579</v>
@@ -44619,7 +44620,7 @@
         <v>576</v>
       </c>
       <c r="BR42" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS42" s="57" t="s">
         <v>580</v>
@@ -44643,13 +44644,13 @@
         <v>576</v>
       </c>
       <c r="CD42" s="28" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="CE42" s="58" t="s">
         <v>582</v>
       </c>
       <c r="CF42" s="28" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="CG42" s="58" t="s">
         <v>583</v>
@@ -44694,25 +44695,25 @@
         <v>507</v>
       </c>
       <c r="DD42" s="70" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="DE42" s="71" t="s">
         <v>509</v>
       </c>
       <c r="DF42" s="70" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="DG42" s="71" t="s">
         <v>511</v>
       </c>
       <c r="DH42" s="70" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="DI42" s="71" t="s">
         <v>512</v>
       </c>
       <c r="DJ42" s="70" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="DK42" s="71" t="s">
         <v>514</v>
@@ -44723,7 +44724,7 @@
         <v>596</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C43" s="48" t="s">
         <v>598</v>
@@ -44735,19 +44736,19 @@
         <v>600</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="G43" s="49" t="s">
         <v>602</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I43" s="49" t="s">
         <v>604</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K43" s="48" t="s">
         <v>605</v>
@@ -44838,7 +44839,7 @@
         <v>596</v>
       </c>
       <c r="BL43" s="41" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="BM43" s="56" t="s">
         <v>600</v>
@@ -44847,7 +44848,7 @@
         <v>596</v>
       </c>
       <c r="BR43" s="27" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="BS43" s="57" t="s">
         <v>602</v>
@@ -44871,13 +44872,13 @@
         <v>596</v>
       </c>
       <c r="CD43" s="28" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="CE43" s="58" t="s">
         <v>605</v>
       </c>
       <c r="CF43" s="28" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="CG43" s="58" t="s">
         <v>606</v>
@@ -44922,13 +44923,13 @@
         <v>538</v>
       </c>
       <c r="DD43" s="46" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="DE43" s="19" t="s">
         <v>540</v>
       </c>
       <c r="DF43" s="46" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="DG43" s="19" t="s">
         <v>542</v>
@@ -44959,13 +44960,13 @@
         <v>630</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G44" s="49" t="s">
         <v>631</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="I44" s="49" t="s">
         <v>632</v>
@@ -44977,7 +44978,7 @@
         <v>633</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M44" s="48" t="s">
         <v>635</v>
@@ -45025,7 +45026,7 @@
         <v>427</v>
       </c>
       <c r="AN44" s="24" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AO44" s="53" t="s">
         <v>429</v>
@@ -45034,25 +45035,25 @@
         <v>417</v>
       </c>
       <c r="AR44" s="25" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="AS44" s="54" t="s">
         <v>419</v>
       </c>
       <c r="AT44" s="25" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AU44" s="54" t="s">
         <v>421</v>
       </c>
       <c r="AV44" s="40" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AW44" s="55" t="s">
         <v>423</v>
       </c>
       <c r="AX44" s="40" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AY44" s="55" t="s">
         <v>425</v>
@@ -45064,7 +45065,7 @@
         <v>427</v>
       </c>
       <c r="BB44" s="25" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="BC44" s="54" t="s">
         <v>429</v>
@@ -45079,7 +45080,7 @@
         <v>629</v>
       </c>
       <c r="BH44" s="41" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="BI44" s="56" t="s">
         <v>630</v>
@@ -45088,7 +45089,7 @@
         <v>627</v>
       </c>
       <c r="BL44" s="41" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="BM44" s="56" t="s">
         <v>630</v>
@@ -45103,7 +45104,7 @@
         <v>631</v>
       </c>
       <c r="BT44" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BU44" s="57" t="s">
         <v>632</v>
@@ -45112,7 +45113,7 @@
         <v>631</v>
       </c>
       <c r="BX44" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BY44" s="57" t="s">
         <v>632</v>
@@ -45121,13 +45122,13 @@
         <v>627</v>
       </c>
       <c r="CD44" s="28" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="CE44" s="58" t="s">
         <v>633</v>
       </c>
       <c r="CF44" s="28" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="CG44" s="58" t="s">
         <v>635</v>
@@ -45168,19 +45169,19 @@
         <v>567</v>
       </c>
       <c r="DD44" s="46" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="DE44" s="19" t="s">
         <v>569</v>
       </c>
       <c r="DF44" s="46" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="DG44" s="19" t="s">
         <v>570</v>
       </c>
       <c r="DH44" s="46" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="DI44" s="19" t="s">
         <v>572</v>
@@ -45195,7 +45196,7 @@
         <v>636</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C45" s="48" t="s">
         <v>636</v>
@@ -45253,7 +45254,7 @@
         <v>461</v>
       </c>
       <c r="AN45" s="24" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AO45" s="53" t="s">
         <v>463</v>
@@ -45268,7 +45269,7 @@
         <v>456</v>
       </c>
       <c r="AT45" s="25" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AU45" s="54" t="s">
         <v>458</v>
@@ -45280,7 +45281,7 @@
         <v>459</v>
       </c>
       <c r="AX45" s="40" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AY45" s="55" t="s">
         <v>460</v>
@@ -45292,7 +45293,7 @@
         <v>461</v>
       </c>
       <c r="BB45" s="25" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="BC45" s="54" t="s">
         <v>463</v>
@@ -45326,7 +45327,7 @@
         <v>636</v>
       </c>
       <c r="CD45" s="28" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="CE45" s="58" t="s">
         <v>636</v>
@@ -45355,7 +45356,7 @@
         <v>730</v>
       </c>
       <c r="CP45" s="29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="CQ45" s="64" t="s">
         <v>732</v>
@@ -45383,25 +45384,25 @@
         <v>589</v>
       </c>
       <c r="DD45" s="46" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="DE45" s="19" t="s">
         <v>590</v>
       </c>
       <c r="DF45" s="46" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="DG45" s="19" t="s">
         <v>591</v>
       </c>
       <c r="DH45" s="46" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="DI45" s="19" t="s">
         <v>592</v>
       </c>
       <c r="DJ45" s="46" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="DK45" s="19" t="s">
         <v>594</v>
@@ -45412,7 +45413,7 @@
         <v>482</v>
       </c>
       <c r="P46" s="23" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="Q46" s="50" t="s">
         <v>743</v>
@@ -45421,7 +45422,7 @@
         <v>482</v>
       </c>
       <c r="AD46" s="24" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AE46" s="53" t="s">
         <v>484</v>
@@ -45433,7 +45434,7 @@
         <v>486</v>
       </c>
       <c r="AH46" s="67" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AI46" s="69" t="s">
         <v>488</v>
@@ -45445,7 +45446,7 @@
         <v>490</v>
       </c>
       <c r="AL46" s="24" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AM46" s="53" t="s">
         <v>491</v>
@@ -45460,37 +45461,37 @@
         <v>482</v>
       </c>
       <c r="AR46" s="25" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AS46" s="54" t="s">
         <v>484</v>
       </c>
       <c r="AT46" s="25" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AU46" s="54" t="s">
         <v>486</v>
       </c>
       <c r="AV46" s="40" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AW46" s="55" t="s">
         <v>488</v>
       </c>
       <c r="AX46" s="40" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AY46" s="55" t="s">
         <v>490</v>
       </c>
       <c r="AZ46" s="25" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="BA46" s="54" t="s">
         <v>491</v>
       </c>
       <c r="BB46" s="25" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="BC46" s="54" t="s">
         <v>492</v>
@@ -45517,7 +45518,7 @@
         <v>618</v>
       </c>
       <c r="CT46" s="70" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="CU46" s="71" t="s">
         <v>620</v>
@@ -45538,13 +45539,13 @@
         <v>618</v>
       </c>
       <c r="DD46" s="70" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="DE46" s="71" t="s">
         <v>620</v>
       </c>
       <c r="DF46" s="70" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="DG46" s="71" t="s">
         <v>622</v>
@@ -45576,7 +45577,7 @@
         <v>519</v>
       </c>
       <c r="P47" s="23" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Q47" s="50" t="s">
         <v>759</v>
@@ -45591,19 +45592,19 @@
         <v>521</v>
       </c>
       <c r="AF47" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AG47" s="53" t="s">
         <v>523</v>
       </c>
       <c r="AH47" s="67" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AI47" s="69" t="s">
         <v>524</v>
       </c>
       <c r="AJ47" s="67" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AK47" s="69" t="s">
         <v>526</v>
@@ -45615,7 +45616,7 @@
         <v>527</v>
       </c>
       <c r="AN47" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AO47" s="53" t="s">
         <v>528</v>
@@ -45624,37 +45625,37 @@
         <v>519</v>
       </c>
       <c r="AR47" s="25" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AS47" s="54" t="s">
         <v>521</v>
       </c>
       <c r="AT47" s="25" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AU47" s="54" t="s">
         <v>523</v>
       </c>
       <c r="AV47" s="40" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AW47" s="55" t="s">
         <v>524</v>
       </c>
       <c r="AX47" s="40" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AY47" s="55" t="s">
         <v>526</v>
       </c>
       <c r="AZ47" s="25" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="BA47" s="54" t="s">
         <v>527</v>
       </c>
       <c r="BB47" s="25" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="BC47" s="54" t="s">
         <v>528</v>
@@ -45701,7 +45702,7 @@
         <v>642</v>
       </c>
       <c r="CT47" s="70" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="CU47" s="71" t="s">
         <v>644</v>
@@ -45722,13 +45723,13 @@
         <v>642</v>
       </c>
       <c r="DD47" s="70" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="DE47" s="71" t="s">
         <v>644</v>
       </c>
       <c r="DF47" s="70" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="DG47" s="71" t="s">
         <v>646</v>
@@ -45760,7 +45761,7 @@
         <v>549</v>
       </c>
       <c r="P48" s="23" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="Q48" s="50" t="s">
         <v>777</v>
@@ -45769,7 +45770,7 @@
         <v>549</v>
       </c>
       <c r="AD48" s="24" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AE48" s="53" t="s">
         <v>551</v>
@@ -45793,7 +45794,7 @@
         <v>554</v>
       </c>
       <c r="AL48" s="24" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AM48" s="53" t="s">
         <v>556</v>
@@ -45808,37 +45809,37 @@
         <v>549</v>
       </c>
       <c r="AR48" s="25" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AS48" s="54" t="s">
         <v>551</v>
       </c>
       <c r="AT48" s="25" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AU48" s="54" t="s">
         <v>552</v>
       </c>
       <c r="AV48" s="40" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AW48" s="55" t="s">
         <v>553</v>
       </c>
       <c r="AX48" s="40" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AY48" s="55" t="s">
         <v>554</v>
       </c>
       <c r="AZ48" s="25" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="BA48" s="54" t="s">
         <v>556</v>
       </c>
       <c r="BB48" s="25" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="BC48" s="54" t="s">
         <v>557</v>
@@ -45853,7 +45854,7 @@
         <v>419</v>
       </c>
       <c r="BH48" s="41" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="BI48" s="56" t="s">
         <v>421</v>
@@ -45868,7 +45869,7 @@
         <v>423</v>
       </c>
       <c r="BT48" s="27" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="BU48" s="57" t="s">
         <v>425</v>
@@ -45915,19 +45916,19 @@
         <v>654</v>
       </c>
       <c r="CV48" s="70" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="CW48" s="71" t="s">
         <v>656</v>
       </c>
       <c r="CX48" s="70" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="CY48" s="71" t="s">
         <v>658</v>
       </c>
       <c r="CZ48" s="70" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="DA48" s="71" t="s">
         <v>660</v>
@@ -45936,13 +45937,13 @@
         <v>652</v>
       </c>
       <c r="DD48" s="70" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="DE48" s="71" t="s">
         <v>654</v>
       </c>
       <c r="DF48" s="70" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="DG48" s="71" t="s">
         <v>656</v>
@@ -45974,7 +45975,7 @@
         <v>576</v>
       </c>
       <c r="P49" s="23" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Q49" s="50" t="s">
         <v>789</v>
@@ -45989,19 +45990,19 @@
         <v>578</v>
       </c>
       <c r="AF49" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AG49" s="53" t="s">
         <v>579</v>
       </c>
       <c r="AH49" s="67" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AI49" s="69" t="s">
         <v>580</v>
       </c>
       <c r="AJ49" s="67" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AK49" s="69" t="s">
         <v>581</v>
@@ -46013,7 +46014,7 @@
         <v>582</v>
       </c>
       <c r="AN49" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AO49" s="53" t="s">
         <v>583</v>
@@ -46022,37 +46023,37 @@
         <v>576</v>
       </c>
       <c r="AR49" s="25" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AS49" s="54" t="s">
         <v>578</v>
       </c>
       <c r="AT49" s="25" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AU49" s="54" t="s">
         <v>579</v>
       </c>
       <c r="AV49" s="40" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AW49" s="55" t="s">
         <v>580</v>
       </c>
       <c r="AX49" s="40" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AY49" s="55" t="s">
         <v>581</v>
       </c>
       <c r="AZ49" s="25" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="BA49" s="54" t="s">
         <v>582</v>
       </c>
       <c r="BB49" s="25" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="BC49" s="54" t="s">
         <v>583</v>
@@ -46061,13 +46062,13 @@
         <v>455</v>
       </c>
       <c r="BF49" s="41" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="BG49" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH49" s="41" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="BI49" s="56" t="s">
         <v>458</v>
@@ -46076,13 +46077,13 @@
         <v>455</v>
       </c>
       <c r="BR49" s="27" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="BS49" s="57" t="s">
         <v>459</v>
       </c>
       <c r="BT49" s="27" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="BU49" s="57" t="s">
         <v>460</v>
@@ -46106,13 +46107,13 @@
         <v>443</v>
       </c>
       <c r="CJ49" s="59" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="CK49" s="60" t="s">
         <v>445</v>
       </c>
       <c r="CL49" s="59" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="CM49" s="60" t="s">
         <v>447</v>
@@ -46134,13 +46135,13 @@
         <v>664</v>
       </c>
       <c r="DD49" s="46" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="DE49" s="19" t="s">
         <v>666</v>
       </c>
       <c r="DF49" s="46" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="DG49" s="19" t="s">
         <v>668</v>
@@ -46172,7 +46173,7 @@
         <v>596</v>
       </c>
       <c r="P50" s="23" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="Q50" s="50" t="s">
         <v>802</v>
@@ -46181,7 +46182,7 @@
         <v>596</v>
       </c>
       <c r="AD50" s="24" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AE50" s="53" t="s">
         <v>598</v>
@@ -46193,7 +46194,7 @@
         <v>600</v>
       </c>
       <c r="AH50" s="67" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="AI50" s="69" t="s">
         <v>602</v>
@@ -46205,7 +46206,7 @@
         <v>604</v>
       </c>
       <c r="AL50" s="24" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AM50" s="53" t="s">
         <v>605</v>
@@ -46220,37 +46221,37 @@
         <v>596</v>
       </c>
       <c r="AR50" s="25" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AS50" s="54" t="s">
         <v>598</v>
       </c>
       <c r="AT50" s="25" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AU50" s="54" t="s">
         <v>600</v>
       </c>
       <c r="AV50" s="40" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="AW50" s="55" t="s">
         <v>602</v>
       </c>
       <c r="AX50" s="40" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="AY50" s="55" t="s">
         <v>604</v>
       </c>
       <c r="AZ50" s="25" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="BA50" s="54" t="s">
         <v>605</v>
       </c>
       <c r="BB50" s="25" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="BC50" s="54" t="s">
         <v>606</v>
@@ -46259,13 +46260,13 @@
         <v>482</v>
       </c>
       <c r="BF50" s="41" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="BG50" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH50" s="41" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="BI50" s="56" t="s">
         <v>486</v>
@@ -46274,13 +46275,13 @@
         <v>482</v>
       </c>
       <c r="BR50" s="27" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="BS50" s="57" t="s">
         <v>488</v>
       </c>
       <c r="BT50" s="27" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="BU50" s="57" t="s">
         <v>490</v>
@@ -46289,7 +46290,7 @@
         <v>482</v>
       </c>
       <c r="CD50" s="28" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="CE50" s="58" t="s">
         <v>491</v>
@@ -46304,13 +46305,13 @@
         <v>470</v>
       </c>
       <c r="CJ50" s="59" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="CK50" s="60" t="s">
         <v>472</v>
       </c>
       <c r="CL50" s="59" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="CM50" s="60" t="s">
         <v>474</v>
@@ -46323,13 +46324,13 @@
         <v>691</v>
       </c>
       <c r="DD50" s="46" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="DE50" s="19" t="s">
         <v>693</v>
       </c>
       <c r="DF50" s="46" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="DG50" s="19" t="s">
         <v>695</v>
@@ -46389,37 +46390,37 @@
         <v>627</v>
       </c>
       <c r="AR51" s="25" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="AS51" s="54" t="s">
         <v>629</v>
       </c>
       <c r="AT51" s="25" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AU51" s="54" t="s">
         <v>630</v>
       </c>
       <c r="AV51" s="40" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AW51" s="55" t="s">
         <v>631</v>
       </c>
       <c r="AX51" s="40" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AY51" s="55" t="s">
         <v>632</v>
       </c>
       <c r="AZ51" s="25" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="BA51" s="54" t="s">
         <v>633</v>
       </c>
       <c r="BB51" s="25" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="BC51" s="54" t="s">
         <v>635</v>
@@ -46428,13 +46429,13 @@
         <v>519</v>
       </c>
       <c r="BF51" s="41" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="BG51" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH51" s="41" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="BI51" s="56" t="s">
         <v>523</v>
@@ -46443,13 +46444,13 @@
         <v>519</v>
       </c>
       <c r="BR51" s="27" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="BS51" s="57" t="s">
         <v>524</v>
       </c>
       <c r="BT51" s="27" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="BU51" s="57" t="s">
         <v>526</v>
@@ -46473,13 +46474,13 @@
         <v>507</v>
       </c>
       <c r="CJ51" s="59" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="CK51" s="60" t="s">
         <v>509</v>
       </c>
       <c r="CL51" s="59" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="CM51" s="60" t="s">
         <v>511</v>
@@ -46511,13 +46512,13 @@
         <v>724</v>
       </c>
       <c r="DD51" s="46" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="DE51" s="19" t="s">
         <v>726</v>
       </c>
       <c r="DF51" s="46" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="DG51" s="19" t="s">
         <v>728</v>
@@ -46562,13 +46563,13 @@
         <v>549</v>
       </c>
       <c r="BF52" s="41" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="BG52" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH52" s="41" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="BI52" s="56" t="s">
         <v>552</v>
@@ -46577,13 +46578,13 @@
         <v>549</v>
       </c>
       <c r="BR52" s="27" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="BS52" s="57" t="s">
         <v>553</v>
       </c>
       <c r="BT52" s="27" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="BU52" s="57" t="s">
         <v>554</v>
@@ -46592,7 +46593,7 @@
         <v>549</v>
       </c>
       <c r="CD52" s="28" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="CE52" s="58" t="s">
         <v>556</v>
@@ -46607,13 +46608,13 @@
         <v>538</v>
       </c>
       <c r="CJ52" s="29" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="CK52" s="64" t="s">
         <v>540</v>
       </c>
       <c r="CL52" s="29" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="CM52" s="64" t="s">
         <v>542</v>
@@ -46626,28 +46627,28 @@
         <v>673</v>
       </c>
       <c r="CT52" s="70" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="CU52" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV52" s="70" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="CW52" s="71" t="s">
         <v>677</v>
       </c>
       <c r="CX52" s="70" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="CY52" s="71" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CZ52" s="70" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="DA52" s="71" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="40.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46730,13 +46731,13 @@
         <v>576</v>
       </c>
       <c r="BF53" s="41" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="BG53" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH53" s="41" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="BI53" s="56" t="s">
         <v>579</v>
@@ -46745,13 +46746,13 @@
         <v>576</v>
       </c>
       <c r="BR53" s="27" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="BS53" s="57" t="s">
         <v>580</v>
       </c>
       <c r="BT53" s="27" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="BU53" s="57" t="s">
         <v>581</v>
@@ -46775,13 +46776,13 @@
         <v>567</v>
       </c>
       <c r="CJ53" s="29" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="CK53" s="64" t="s">
         <v>569</v>
       </c>
       <c r="CL53" s="29" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="CM53" s="64" t="s">
         <v>570</v>
@@ -46794,28 +46795,28 @@
         <v>700</v>
       </c>
       <c r="CT53" s="70" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="CU53" s="71" t="s">
         <v>701</v>
       </c>
       <c r="CV53" s="70" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="CW53" s="71" t="s">
         <v>703</v>
       </c>
       <c r="CX53" s="70" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="CY53" s="71" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CZ53" s="70" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="DA53" s="71" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="69.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -46836,7 +46837,7 @@
         <v>417</v>
       </c>
       <c r="P54" s="23" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="Q54" s="50" t="s">
         <v>423</v>
@@ -46846,37 +46847,37 @@
         <v>417</v>
       </c>
       <c r="AD54" s="24" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="AE54" s="53" t="s">
         <v>419</v>
       </c>
       <c r="AF54" s="24" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="AG54" s="53" t="s">
         <v>421</v>
       </c>
       <c r="AH54" s="67" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AI54" s="69" t="s">
         <v>423</v>
       </c>
       <c r="AJ54" s="67" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AK54" s="69" t="s">
         <v>425</v>
       </c>
       <c r="AL54" s="24" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AM54" s="53" t="s">
         <v>427</v>
       </c>
       <c r="AN54" s="24" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AO54" s="53" t="s">
         <v>429</v>
@@ -46924,13 +46925,13 @@
         <v>596</v>
       </c>
       <c r="BF54" s="41" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="BG54" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH54" s="41" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="BI54" s="56" t="s">
         <v>600</v>
@@ -46939,13 +46940,13 @@
         <v>596</v>
       </c>
       <c r="BR54" s="27" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="BS54" s="57" t="s">
         <v>602</v>
       </c>
       <c r="BT54" s="27" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="BU54" s="57" t="s">
         <v>604</v>
@@ -46954,7 +46955,7 @@
         <v>596</v>
       </c>
       <c r="CD54" s="28" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="CE54" s="58" t="s">
         <v>605</v>
@@ -46969,13 +46970,13 @@
         <v>589</v>
       </c>
       <c r="CJ54" s="29" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="CK54" s="64" t="s">
         <v>590</v>
       </c>
       <c r="CL54" s="29" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="CM54" s="64" t="s">
         <v>591</v>
@@ -46988,28 +46989,28 @@
         <v>733</v>
       </c>
       <c r="CT54" s="70" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="CU54" s="71" t="s">
         <v>735</v>
       </c>
       <c r="CV54" s="70" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="CW54" s="71" t="s">
         <v>737</v>
       </c>
       <c r="CX54" s="70" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="CY54" s="71" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CZ54" s="70" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="DA54" s="71" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="54.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47040,37 +47041,37 @@
         <v>455</v>
       </c>
       <c r="AD55" s="24" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AE55" s="53" t="s">
         <v>456</v>
       </c>
       <c r="AF55" s="24" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AG55" s="53" t="s">
         <v>458</v>
       </c>
       <c r="AH55" s="67" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AI55" s="69" t="s">
         <v>459</v>
       </c>
       <c r="AJ55" s="67" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AK55" s="69" t="s">
         <v>460</v>
       </c>
       <c r="AL55" s="24" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AM55" s="53" t="s">
         <v>461</v>
       </c>
       <c r="AN55" s="24" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AO55" s="53" t="s">
         <v>463</v>
@@ -47109,7 +47110,7 @@
         <v>461</v>
       </c>
       <c r="BB55" s="25" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="BC55" s="54" t="s">
         <v>463</v>
@@ -47118,13 +47119,13 @@
         <v>627</v>
       </c>
       <c r="BF55" s="41" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="BG55" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH55" s="41" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="BI55" s="56" t="s">
         <v>630</v>
@@ -47133,13 +47134,13 @@
         <v>627</v>
       </c>
       <c r="BR55" s="27" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="BS55" s="57" t="s">
         <v>631</v>
       </c>
       <c r="BT55" s="27" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="BU55" s="57" t="s">
         <v>632</v>
@@ -47224,37 +47225,37 @@
         <v>482</v>
       </c>
       <c r="AD56" s="24" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="AE56" s="53" t="s">
         <v>484</v>
       </c>
       <c r="AF56" s="24" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="AG56" s="53" t="s">
         <v>486</v>
       </c>
       <c r="AH56" s="67" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="AI56" s="69" t="s">
         <v>488</v>
       </c>
       <c r="AJ56" s="67" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="AK56" s="69" t="s">
         <v>490</v>
       </c>
       <c r="AL56" s="24" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="AM56" s="53" t="s">
         <v>491</v>
       </c>
       <c r="AN56" s="24" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="AO56" s="53" t="s">
         <v>492</v>
@@ -47263,7 +47264,7 @@
         <v>482</v>
       </c>
       <c r="AR56" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AS56" s="54" t="s">
         <v>484</v>
@@ -47287,7 +47288,7 @@
         <v>490</v>
       </c>
       <c r="AZ56" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="BA56" s="54" t="s">
         <v>491</v>
@@ -47302,7 +47303,7 @@
         <v>636</v>
       </c>
       <c r="BF56" s="41" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="BG56" s="56" t="s">
         <v>636</v>
@@ -47313,7 +47314,7 @@
         <v>636</v>
       </c>
       <c r="BR56" s="27" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="BS56" s="57" t="s">
         <v>636</v>
@@ -47380,37 +47381,37 @@
         <v>519</v>
       </c>
       <c r="AD57" s="24" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="AE57" s="53" t="s">
         <v>521</v>
       </c>
       <c r="AF57" s="24" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="AG57" s="53" t="s">
         <v>523</v>
       </c>
       <c r="AH57" s="67" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="AI57" s="69" t="s">
         <v>524</v>
       </c>
       <c r="AJ57" s="67" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="AK57" s="69" t="s">
         <v>526</v>
       </c>
       <c r="AL57" s="24" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="AM57" s="53" t="s">
         <v>527</v>
       </c>
       <c r="AN57" s="24" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="AO57" s="53" t="s">
         <v>528</v>
@@ -47467,7 +47468,7 @@
         <v>652</v>
       </c>
       <c r="CJ57" s="59" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="CK57" s="60" t="s">
         <v>654</v>
@@ -47556,19 +47557,19 @@
         <v>551</v>
       </c>
       <c r="AF58" s="24" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="AG58" s="53" t="s">
         <v>552</v>
       </c>
       <c r="AH58" s="67" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="AI58" s="69" t="s">
         <v>553</v>
       </c>
       <c r="AJ58" s="67" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="AK58" s="69" t="s">
         <v>554</v>
@@ -47578,7 +47579,7 @@
         <v>556</v>
       </c>
       <c r="AN58" s="24" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="AO58" s="53" t="s">
         <v>557</v>
@@ -47677,31 +47678,31 @@
         <v>672</v>
       </c>
       <c r="CS58" s="70" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="CT58" s="70" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="CU58" s="71" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="CV58" s="70" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="CW58" s="71" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="CX58" s="70" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="CY58" s="71" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="CZ58" s="70" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="DA58" s="71" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47715,19 +47716,19 @@
         <v>419</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>421</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="G59" s="49" t="s">
         <v>423</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="I59" s="49" t="s">
         <v>425</v>
@@ -47758,37 +47759,37 @@
         <v>576</v>
       </c>
       <c r="AD59" s="24" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="AE59" s="53" t="s">
         <v>578</v>
       </c>
       <c r="AF59" s="24" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="AG59" s="53" t="s">
         <v>579</v>
       </c>
       <c r="AH59" s="67" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="AI59" s="69" t="s">
         <v>580</v>
       </c>
       <c r="AJ59" s="67" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="AK59" s="69" t="s">
         <v>581</v>
       </c>
       <c r="AL59" s="24" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="AM59" s="53" t="s">
         <v>582</v>
       </c>
       <c r="AN59" s="24" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="AO59" s="53" t="s">
         <v>583</v>
@@ -47851,13 +47852,13 @@
         <v>417</v>
       </c>
       <c r="BR59" s="27" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="BS59" s="57" t="s">
         <v>423</v>
       </c>
       <c r="BT59" s="27" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="BU59" s="57" t="s">
         <v>425</v>
@@ -47895,31 +47896,31 @@
         <v>699</v>
       </c>
       <c r="CS59" s="70" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="CT59" s="70" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="CU59" s="71" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="CV59" s="70" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="CW59" s="71" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="CX59" s="70" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="CY59" s="71" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="CZ59" s="70" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="DA59" s="71" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -47933,7 +47934,7 @@
         <v>456</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>458</v>
@@ -47945,7 +47946,7 @@
         <v>459</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="I60" s="49" t="s">
         <v>460</v>
@@ -47976,37 +47977,37 @@
         <v>596</v>
       </c>
       <c r="AD60" s="24" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="AE60" s="53" t="s">
         <v>598</v>
       </c>
       <c r="AF60" s="24" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="AG60" s="53" t="s">
         <v>600</v>
       </c>
       <c r="AH60" s="67" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="AI60" s="69" t="s">
         <v>602</v>
       </c>
       <c r="AJ60" s="67" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="AK60" s="69" t="s">
         <v>604</v>
       </c>
       <c r="AL60" s="24" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="AM60" s="53" t="s">
         <v>605</v>
       </c>
       <c r="AN60" s="24" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="AO60" s="53" t="s">
         <v>606</v>
@@ -48054,7 +48055,7 @@
         <v>455</v>
       </c>
       <c r="BF60" s="41" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="BG60" s="56" t="s">
         <v>456</v>
@@ -48069,13 +48070,13 @@
         <v>455</v>
       </c>
       <c r="BR60" s="27" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="BS60" s="57" t="s">
         <v>459</v>
       </c>
       <c r="BT60" s="27" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="BU60" s="57" t="s">
         <v>460</v>
@@ -48107,37 +48108,37 @@
         <v>730</v>
       </c>
       <c r="CP60" s="29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="CQ60" s="64" t="s">
         <v>732</v>
       </c>
       <c r="CS60" s="70" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="CT60" s="70" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="CU60" s="71" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="CV60" s="70" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="CW60" s="71" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="CX60" s="70" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="CY60" s="71" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="CZ60" s="70" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="DA60" s="71" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="41.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48145,37 +48146,37 @@
         <v>482</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C61" s="48" t="s">
         <v>484</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>486</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G61" s="49" t="s">
         <v>488</v>
       </c>
       <c r="H61" s="21" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="I61" s="49" t="s">
         <v>490</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K61" s="48" t="s">
         <v>491</v>
       </c>
       <c r="L61" s="21" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="M61" s="48" t="s">
         <v>492</v>
@@ -48233,7 +48234,7 @@
         <v>482</v>
       </c>
       <c r="BF61" s="41" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="BG61" s="56" t="s">
         <v>484</v>
@@ -48248,13 +48249,13 @@
         <v>482</v>
       </c>
       <c r="BR61" s="27" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BS61" s="57" t="s">
         <v>488</v>
       </c>
       <c r="BT61" s="27" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="BU61" s="57" t="s">
         <v>490</v>
@@ -48294,13 +48295,13 @@
         <v>521</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E62" s="48" t="s">
         <v>523</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G62" s="49" t="s">
         <v>524</v>
@@ -48347,7 +48348,7 @@
         <v>519</v>
       </c>
       <c r="BF62" s="41" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="BG62" s="56" t="s">
         <v>521</v>
@@ -48362,13 +48363,13 @@
         <v>519</v>
       </c>
       <c r="BR62" s="27" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BS62" s="57" t="s">
         <v>524</v>
       </c>
       <c r="BT62" s="27" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="BU62" s="57" t="s">
         <v>526</v>
@@ -48389,7 +48390,7 @@
         <v>549</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>1231</v>
+        <v>1041</v>
       </c>
       <c r="C63" s="48" t="s">
         <v>551</v>
@@ -48401,7 +48402,7 @@
         <v>552</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G63" s="49" t="s">
         <v>553</v>
@@ -48413,7 +48414,7 @@
         <v>554</v>
       </c>
       <c r="J63" s="21" t="s">
-        <v>1231</v>
+        <v>1041</v>
       </c>
       <c r="K63" s="48" t="s">
         <v>556</v>
@@ -48510,13 +48511,13 @@
         <v>549</v>
       </c>
       <c r="BR63" s="27" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BS63" s="57" t="s">
         <v>553</v>
       </c>
       <c r="BT63" s="27" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="BU63" s="57" t="s">
         <v>554</v>
@@ -48585,7 +48586,7 @@
         <v>579</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G64" s="49" t="s">
         <v>580</v>
@@ -48707,7 +48708,7 @@
         <v>576</v>
       </c>
       <c r="BF64" s="41" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="BG64" s="56" t="s">
         <v>578</v>
@@ -48722,13 +48723,13 @@
         <v>576</v>
       </c>
       <c r="BR64" s="27" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BS64" s="57" t="s">
         <v>580</v>
       </c>
       <c r="BT64" s="27" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="BU64" s="57" t="s">
         <v>581</v>
@@ -48757,13 +48758,13 @@
         <v>1240</v>
       </c>
       <c r="CO64" s="60" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CP64" s="59" t="s">
         <v>1241</v>
       </c>
       <c r="CQ64" s="60" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="CS64" s="70" t="s">
         <v>673</v>
@@ -48781,19 +48782,19 @@
         <v>677</v>
       </c>
       <c r="CY64" s="70" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="CZ64" s="70" t="s">
         <v>1244</v>
       </c>
       <c r="DA64" s="71" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="DB64" s="70" t="s">
         <v>1245</v>
       </c>
       <c r="DC64" s="71" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="97.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -48807,7 +48808,7 @@
         <v>598</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>600</v>
@@ -48831,7 +48832,7 @@
         <v>605</v>
       </c>
       <c r="L65" s="21" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="M65" s="48" t="s">
         <v>606</v>
@@ -48985,13 +48986,13 @@
         <v>1255</v>
       </c>
       <c r="CO65" s="60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CP65" s="59" t="s">
         <v>1256</v>
       </c>
       <c r="CQ65" s="60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="CS65" s="70" t="s">
         <v>700</v>
@@ -49009,19 +49010,19 @@
         <v>703</v>
       </c>
       <c r="CY65" s="70" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="CZ65" s="70" t="s">
         <v>1259</v>
       </c>
       <c r="DA65" s="71" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="DB65" s="70" t="s">
         <v>1260</v>
       </c>
       <c r="DC65" s="71" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="68.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49035,7 +49036,7 @@
         <v>629</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E66" s="48" t="s">
         <v>630</v>
@@ -49047,7 +49048,7 @@
         <v>631</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="I66" s="49" t="s">
         <v>632</v>
@@ -49124,7 +49125,7 @@
         <v>482</v>
       </c>
       <c r="AR66" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AS66" s="54" t="s">
         <v>484</v>
@@ -49148,7 +49149,7 @@
         <v>490</v>
       </c>
       <c r="AZ66" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="BA66" s="54" t="s">
         <v>491</v>
@@ -49213,13 +49214,13 @@
         <v>1267</v>
       </c>
       <c r="CO66" s="60" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CP66" s="59" t="s">
         <v>1268</v>
       </c>
       <c r="CQ66" s="60" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="CS66" s="70" t="s">
         <v>733</v>
@@ -49237,19 +49238,19 @@
         <v>737</v>
       </c>
       <c r="CY66" s="70" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="CZ66" s="70" t="s">
         <v>1271</v>
       </c>
       <c r="DA66" s="71" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="DB66" s="70" t="s">
         <v>1272</v>
       </c>
       <c r="DC66" s="71" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49382,7 +49383,7 @@
         <v>636</v>
       </c>
       <c r="BR67" s="27" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="BS67" s="57" t="s">
         <v>636</v>
@@ -49861,7 +49862,7 @@
         <v>419</v>
       </c>
       <c r="BH70" s="41" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="BI70" s="56" t="s">
         <v>421</v>
@@ -49876,7 +49877,7 @@
         <v>423</v>
       </c>
       <c r="BT70" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BU70" s="57" t="s">
         <v>425</v>
@@ -49911,11 +49912,11 @@
         <v>1254</v>
       </c>
       <c r="CO70" s="60" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CP70" s="59"/>
       <c r="CQ70" s="60" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="CS70" s="70" t="s">
         <v>1286</v>
@@ -50035,7 +50036,7 @@
         <v>456</v>
       </c>
       <c r="BH71" s="41" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="BI71" s="56" t="s">
         <v>458</v>
@@ -50050,7 +50051,7 @@
         <v>459</v>
       </c>
       <c r="BT71" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BU71" s="57" t="s">
         <v>460</v>
@@ -50083,11 +50084,11 @@
       </c>
       <c r="CN71" s="59"/>
       <c r="CO71" s="60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CP71" s="59"/>
       <c r="CQ71" s="60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="CS71" s="70" t="s">
         <v>1294</v>
@@ -50175,7 +50176,7 @@
         <v>482</v>
       </c>
       <c r="BR72" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS72" s="57" t="s">
         <v>488</v>
@@ -50214,11 +50215,11 @@
       </c>
       <c r="CN72" s="59"/>
       <c r="CO72" s="60" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CP72" s="59"/>
       <c r="CQ72" s="60" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="CS72" s="70" t="s">
         <v>1299</v>
@@ -50341,7 +50342,7 @@
         <v>519</v>
       </c>
       <c r="BR73" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS73" s="57" t="s">
         <v>524</v>
@@ -50505,7 +50506,7 @@
         <v>549</v>
       </c>
       <c r="BR74" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS74" s="57" t="s">
         <v>553</v>
@@ -50583,7 +50584,7 @@
         <v>461</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="S75" s="50" t="s">
         <v>463</v>
@@ -50664,7 +50665,7 @@
         <v>576</v>
       </c>
       <c r="BR75" s="27" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="BS75" s="57" t="s">
         <v>580</v>
@@ -50761,7 +50762,7 @@
         <v>482</v>
       </c>
       <c r="P76" s="23" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="Q76" s="50" t="s">
         <v>491</v>
@@ -50794,7 +50795,7 @@
         <v>482</v>
       </c>
       <c r="AR76" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AS76" s="54" t="s">
         <v>484</v>
@@ -50818,7 +50819,7 @@
         <v>490</v>
       </c>
       <c r="AZ76" s="25" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="BA76" s="54" t="s">
         <v>491</v>
@@ -50848,7 +50849,7 @@
         <v>596</v>
       </c>
       <c r="BR76" s="27" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="BS76" s="57" t="s">
         <v>602</v>
@@ -50889,11 +50890,11 @@
         <v>1314</v>
       </c>
       <c r="CO76" s="60" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CP76" s="59"/>
       <c r="CQ76" s="60" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="CS76" s="70" t="s">
         <v>673</v>
@@ -51033,7 +51034,7 @@
         <v>629</v>
       </c>
       <c r="BH77" s="41" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="BI77" s="56" t="s">
         <v>630</v>
@@ -51048,7 +51049,7 @@
         <v>631</v>
       </c>
       <c r="BT77" s="27" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="BU77" s="57" t="s">
         <v>632</v>
@@ -51083,11 +51084,11 @@
         <v>1320</v>
       </c>
       <c r="CO77" s="60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CP77" s="59"/>
       <c r="CQ77" s="60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="CS77" s="70" t="s">
         <v>700</v>
@@ -51245,11 +51246,11 @@
         <v>1322</v>
       </c>
       <c r="CO78" s="60" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CP78" s="59"/>
       <c r="CQ78" s="60" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="CS78" s="70" t="s">
         <v>733</v>
@@ -51797,31 +51798,31 @@
       <c r="CF82" s="22"/>
       <c r="CG82" s="22"/>
       <c r="CI82" s="59" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="CJ82" s="59" t="s">
         <v>422</v>
       </c>
       <c r="CK82" s="60" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="CL82" s="59" t="s">
         <v>1338</v>
       </c>
       <c r="CM82" s="60" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="CN82" s="59" t="s">
         <v>1339</v>
       </c>
       <c r="CO82" s="60" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="CP82" s="59" t="s">
         <v>1340</v>
       </c>
       <c r="CQ82" s="73" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="CS82" s="70" t="s">
         <v>618</v>
@@ -51852,7 +51853,7 @@
         <v>482</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C83" s="48" t="s">
         <v>484</v>
@@ -51876,7 +51877,7 @@
         <v>490</v>
       </c>
       <c r="J83" s="21" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K83" s="48" t="s">
         <v>491</v>
@@ -51954,7 +51955,7 @@
         <v>482</v>
       </c>
       <c r="BF83" s="41" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="BG83" s="56" t="s">
         <v>484</v>
@@ -51992,31 +51993,31 @@
       <c r="CF83" s="22"/>
       <c r="CG83" s="22"/>
       <c r="CI83" s="59" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="CJ83" s="59" t="s">
         <v>1276</v>
       </c>
       <c r="CK83" s="60" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="CL83" s="59" t="s">
         <v>479</v>
       </c>
       <c r="CM83" s="60" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="CN83" s="59" t="s">
         <v>475</v>
       </c>
       <c r="CO83" s="73" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="CP83" s="59" t="s">
         <v>1347</v>
       </c>
       <c r="CQ83" s="73" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="CS83" s="70" t="s">
         <v>642</v>
@@ -52211,31 +52212,31 @@
       <c r="CF84" s="22"/>
       <c r="CG84" s="22"/>
       <c r="CI84" s="59" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="CJ84" s="59" t="s">
         <v>1362</v>
       </c>
       <c r="CK84" s="60" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="CL84" s="59" t="s">
         <v>1363</v>
       </c>
       <c r="CM84" s="60" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="CN84" s="59" t="s">
         <v>194</v>
       </c>
       <c r="CO84" s="73" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="CP84" s="59" t="s">
         <v>1364</v>
       </c>
       <c r="CQ84" s="73" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="CS84" s="70" t="s">
         <v>652</v>
@@ -52270,7 +52271,7 @@
         <v>549</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C85" s="48" t="s">
         <v>551</v>
@@ -52294,7 +52295,7 @@
         <v>554</v>
       </c>
       <c r="J85" s="21" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K85" s="48" t="s">
         <v>556</v>
@@ -52461,7 +52462,7 @@
         <v>578</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E86" s="48" t="s">
         <v>579</v>
@@ -52485,7 +52486,7 @@
         <v>582</v>
       </c>
       <c r="L86" s="21" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="M86" s="48" t="s">
         <v>583</v>
@@ -52633,7 +52634,7 @@
         <v>598</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E87" s="48" t="s">
         <v>600</v>
@@ -52657,7 +52658,7 @@
         <v>605</v>
       </c>
       <c r="L87" s="21" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="M87" s="48" t="s">
         <v>606</v>
@@ -52757,7 +52758,7 @@
         <v>598</v>
       </c>
       <c r="BH87" s="41" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="BI87" s="56" t="s">
         <v>600</v>
@@ -53382,20 +53383,16 @@
       </c>
       <c r="M91" s="21"/>
       <c r="O91" s="27" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="P91" s="27" t="s">
         <v>720</v>
       </c>
       <c r="Q91" s="57" t="s">
-        <v>631</v>
-      </c>
-      <c r="R91" s="27" t="s">
-        <v>721</v>
-      </c>
-      <c r="S91" s="57" t="s">
-        <v>632</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="R91" s="27"/>
+      <c r="S91" s="42"/>
       <c r="T91" s="22"/>
       <c r="V91" s="22"/>
       <c r="X91" s="22"/>
@@ -53540,17 +53537,8 @@
       <c r="M92" s="48" t="s">
         <v>429</v>
       </c>
-      <c r="O92" s="27" t="s">
-        <v>636</v>
-      </c>
-      <c r="P92" s="27" t="s">
-        <v>720</v>
-      </c>
-      <c r="Q92" s="57" t="s">
-        <v>636</v>
-      </c>
-      <c r="R92" s="27"/>
-      <c r="S92" s="42"/>
+      <c r="P92" s="22"/>
+      <c r="R92" s="22"/>
       <c r="T92" s="22"/>
       <c r="V92" s="22"/>
       <c r="X92" s="22"/>
@@ -53938,7 +53926,7 @@
         <v>482</v>
       </c>
       <c r="CD94" s="28" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="CE94" s="58" t="s">
         <v>491</v>
@@ -55421,7 +55409,7 @@
         <v>730</v>
       </c>
       <c r="CP102" s="59" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="CQ102" s="60" t="s">
         <v>732</v>
@@ -55650,7 +55638,7 @@
         <v>427</v>
       </c>
       <c r="AN104" s="24" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AO104" s="53" t="s">
         <v>429</v>
@@ -55706,7 +55694,7 @@
         <v>482</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C105" s="48" t="s">
         <v>484</v>
@@ -55730,7 +55718,7 @@
         <v>490</v>
       </c>
       <c r="J105" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K105" s="48" t="s">
         <v>491</v>
@@ -55781,7 +55769,7 @@
         <v>461</v>
       </c>
       <c r="AN105" s="24" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AO105" s="53" t="s">
         <v>463</v>
@@ -55915,7 +55903,7 @@
         <v>482</v>
       </c>
       <c r="AD106" s="24" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AE106" s="53" t="s">
         <v>484</v>
@@ -55939,7 +55927,7 @@
         <v>490</v>
       </c>
       <c r="AL106" s="24" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AM106" s="53" t="s">
         <v>491</v>
@@ -56101,7 +56089,7 @@
         <v>521</v>
       </c>
       <c r="AF107" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AG107" s="53" t="s">
         <v>523</v>
@@ -56113,7 +56101,7 @@
         <v>524</v>
       </c>
       <c r="AJ107" s="67" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AK107" s="69" t="s">
         <v>526</v>
@@ -56125,7 +56113,7 @@
         <v>527</v>
       </c>
       <c r="AN107" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AO107" s="53" t="s">
         <v>528</v>
@@ -56275,7 +56263,7 @@
         <v>549</v>
       </c>
       <c r="AD108" s="24" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AE108" s="53" t="s">
         <v>551</v>
@@ -56299,7 +56287,7 @@
         <v>554</v>
       </c>
       <c r="AL108" s="24" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AM108" s="53" t="s">
         <v>556</v>
@@ -56461,7 +56449,7 @@
         <v>578</v>
       </c>
       <c r="AF109" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AG109" s="53" t="s">
         <v>579</v>
@@ -56473,7 +56461,7 @@
         <v>580</v>
       </c>
       <c r="AJ109" s="67" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AK109" s="69" t="s">
         <v>581</v>
@@ -56485,7 +56473,7 @@
         <v>582</v>
       </c>
       <c r="AN109" s="24" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AO109" s="53" t="s">
         <v>583</v>
@@ -56617,7 +56605,7 @@
         <v>596</v>
       </c>
       <c r="AD110" s="24" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AE110" s="53" t="s">
         <v>598</v>
@@ -56629,7 +56617,7 @@
         <v>600</v>
       </c>
       <c r="AH110" s="67" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="AI110" s="69" t="s">
         <v>602</v>
@@ -56641,7 +56629,7 @@
         <v>604</v>
       </c>
       <c r="AL110" s="24" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AM110" s="53" t="s">
         <v>605</v>
@@ -56904,13 +56892,13 @@
         <v>1240</v>
       </c>
       <c r="CO112" s="60" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CP112" s="59" t="s">
         <v>1284</v>
       </c>
       <c r="CQ112" s="60" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="CS112" s="70" t="s">
         <v>618</v>
@@ -57052,13 +57040,13 @@
         <v>1581</v>
       </c>
       <c r="CO113" s="60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CP113" s="59" t="s">
         <v>1256</v>
       </c>
       <c r="CQ113" s="60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="CS113" s="70" t="s">
         <v>642</v>
@@ -57232,13 +57220,13 @@
         <v>1602</v>
       </c>
       <c r="CO114" s="60" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CP114" s="59" t="s">
         <v>1603</v>
       </c>
       <c r="CQ114" s="60" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="CS114" s="70" t="s">
         <v>652</v>
@@ -58080,7 +58068,7 @@
         <v>596</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C120" s="48" t="s">
         <v>598</v>
@@ -58814,7 +58802,7 @@
         <v>419</v>
       </c>
       <c r="BH125" s="41" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="BI125" s="56" t="s">
         <v>421</v>
@@ -58988,13 +58976,13 @@
         <v>455</v>
       </c>
       <c r="BF126" s="41" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="BG126" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH126" s="41" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="BI126" s="56" t="s">
         <v>458</v>
@@ -59328,7 +59316,7 @@
         <v>519</v>
       </c>
       <c r="BF128" s="41" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="BG128" s="56" t="s">
         <v>521</v>
@@ -59649,7 +59637,7 @@
         <v>576</v>
       </c>
       <c r="BF130" s="41" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="BG130" s="56" t="s">
         <v>578</v>
@@ -59809,7 +59797,7 @@
         <v>596</v>
       </c>
       <c r="BF131" s="41" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="BG131" s="56" t="s">
         <v>598</v>
@@ -59854,7 +59842,7 @@
         <v>646</v>
       </c>
       <c r="CN131" s="59" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="CO131" s="60" t="s">
         <v>648</v>
@@ -59963,7 +59951,7 @@
         <v>629</v>
       </c>
       <c r="BH132" s="41" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="BI132" s="56" t="s">
         <v>630</v>
@@ -60378,13 +60366,13 @@
         <v>422</v>
       </c>
       <c r="CO136" s="60" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CP136" s="59" t="s">
         <v>1284</v>
       </c>
       <c r="CQ136" s="60" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="CS136" s="70" t="s">
         <v>673</v>
@@ -60514,13 +60502,13 @@
         <v>1809</v>
       </c>
       <c r="CO137" s="60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CP137" s="59" t="s">
         <v>1256</v>
       </c>
       <c r="CQ137" s="60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="CS137" s="70" t="s">
         <v>700</v>
@@ -60538,7 +60526,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="54.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="41.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="21" t="s">
         <v>455</v>
       </c>
@@ -60650,13 +60638,13 @@
         <v>1602</v>
       </c>
       <c r="CO138" s="60" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CP138" s="59" t="s">
         <v>1603</v>
       </c>
       <c r="CQ138" s="60" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="CS138" s="70" t="s">
         <v>733</v>
@@ -60679,7 +60667,7 @@
         <v>482</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C139" s="48" t="s">
         <v>484</v>
@@ -60703,7 +60691,7 @@
         <v>490</v>
       </c>
       <c r="J139" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K139" s="48" t="s">
         <v>491</v>
@@ -60861,7 +60849,7 @@
         <v>549</v>
       </c>
       <c r="BR140" s="27" t="s">
-        <v>1825</v>
+        <v>1814</v>
       </c>
       <c r="BS140" s="57" t="s">
         <v>553</v>
@@ -60940,7 +60928,7 @@
         <v>576</v>
       </c>
       <c r="BF141" s="41" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="BG141" s="56" t="s">
         <v>578</v>
@@ -60955,7 +60943,7 @@
         <v>576</v>
       </c>
       <c r="BR141" s="27" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="BS141" s="57" t="s">
         <v>580</v>
@@ -61072,13 +61060,13 @@
         <v>596</v>
       </c>
       <c r="BF142" s="41" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="BG142" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH142" s="41" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="BI142" s="56" t="s">
         <v>600</v>
@@ -61087,13 +61075,13 @@
         <v>596</v>
       </c>
       <c r="BR142" s="27" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="BS142" s="57" t="s">
         <v>602</v>
       </c>
       <c r="BT142" s="27" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="BU142" s="57" t="s">
         <v>604</v>
@@ -61111,7 +61099,7 @@
         <v>675</v>
       </c>
       <c r="CL142" s="59" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="CM142" s="60" t="s">
         <v>677</v>
@@ -61120,37 +61108,37 @@
         <v>1240</v>
       </c>
       <c r="CO142" s="60" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="CP142" s="59" t="s">
         <v>1284</v>
       </c>
       <c r="CQ142" s="60" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="CS142" s="70" t="s">
         <v>443</v>
       </c>
       <c r="CT142" s="70" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="CU142" s="71" t="s">
         <v>445</v>
       </c>
       <c r="CV142" s="70" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="CW142" s="71" t="s">
         <v>447</v>
       </c>
       <c r="CX142" s="70" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="CY142" s="71" t="s">
         <v>449</v>
       </c>
       <c r="CZ142" s="70" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="DA142" s="71" t="s">
         <v>451</v>
@@ -61179,7 +61167,7 @@
         <v>602</v>
       </c>
       <c r="H143" s="37" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="I143" s="49" t="s">
         <v>604</v>
@@ -61220,13 +61208,13 @@
         <v>627</v>
       </c>
       <c r="BF143" s="41" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="BG143" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH143" s="41" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="BI143" s="56" t="s">
         <v>630</v>
@@ -61235,13 +61223,13 @@
         <v>627</v>
       </c>
       <c r="BR143" s="27" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="BS143" s="57" t="s">
         <v>631</v>
       </c>
       <c r="BT143" s="27" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="BU143" s="57" t="s">
         <v>632</v>
@@ -61268,37 +61256,37 @@
         <v>1809</v>
       </c>
       <c r="CO143" s="60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="CP143" s="59" t="s">
         <v>1256</v>
       </c>
       <c r="CQ143" s="60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="CS143" s="70" t="s">
         <v>470</v>
       </c>
       <c r="CT143" s="70" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="CU143" s="71" t="s">
         <v>472</v>
       </c>
       <c r="CV143" s="70" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="CW143" s="71" t="s">
         <v>474</v>
       </c>
       <c r="CX143" s="70" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="CY143" s="71" t="s">
         <v>476</v>
       </c>
       <c r="CZ143" s="70" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="DA143" s="71" t="s">
         <v>478</v>
@@ -61368,7 +61356,7 @@
         <v>636</v>
       </c>
       <c r="BF144" s="41" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="BG144" s="56" t="s">
         <v>636</v>
@@ -61379,7 +61367,7 @@
         <v>636</v>
       </c>
       <c r="BR144" s="27" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="BS144" s="57" t="s">
         <v>636</v>
@@ -61408,37 +61396,37 @@
         <v>1602</v>
       </c>
       <c r="CO144" s="60" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="CP144" s="59" t="s">
         <v>1603</v>
       </c>
       <c r="CQ144" s="60" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="CS144" s="70" t="s">
         <v>507</v>
       </c>
       <c r="CT144" s="70" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="CU144" s="71" t="s">
         <v>509</v>
       </c>
       <c r="CV144" s="70" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="CW144" s="71" t="s">
         <v>511</v>
       </c>
       <c r="CX144" s="70" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="CY144" s="71" t="s">
         <v>512</v>
       </c>
       <c r="CZ144" s="70" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="DA144" s="71" t="s">
         <v>514</v>
@@ -61506,25 +61494,25 @@
         <v>538</v>
       </c>
       <c r="CT145" s="46" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="CU145" s="19" t="s">
         <v>540</v>
       </c>
       <c r="CV145" s="46" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="CW145" s="19" t="s">
         <v>542</v>
       </c>
       <c r="CX145" s="46" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="CY145" s="19" t="s">
         <v>544</v>
       </c>
       <c r="CZ145" s="46" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="DA145" s="19" t="s">
         <v>546</v>
@@ -61605,25 +61593,25 @@
         <v>567</v>
       </c>
       <c r="CT146" s="46" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="CU146" s="19" t="s">
         <v>569</v>
       </c>
       <c r="CV146" s="46" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="CW146" s="19" t="s">
         <v>570</v>
       </c>
       <c r="CX146" s="46" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="CY146" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CZ146" s="46" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="DA146" s="19" t="s">
         <v>574</v>
@@ -61714,25 +61702,25 @@
         <v>1646</v>
       </c>
       <c r="CJ147" s="59" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="CK147" s="60" t="s">
         <v>1648</v>
       </c>
       <c r="CL147" s="59" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="CM147" s="60" t="s">
         <v>1650</v>
       </c>
       <c r="CN147" s="59" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="CO147" s="73" t="s">
         <v>1651</v>
       </c>
       <c r="CP147" s="59" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="CQ147" s="73" t="s">
         <v>1653</v>
@@ -61741,25 +61729,25 @@
         <v>589</v>
       </c>
       <c r="CT147" s="46" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="CU147" s="19" t="s">
         <v>590</v>
       </c>
       <c r="CV147" s="46" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="CW147" s="19" t="s">
         <v>591</v>
       </c>
       <c r="CX147" s="46" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="CY147" s="19" t="s">
         <v>592</v>
       </c>
       <c r="CZ147" s="46" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="DA147" s="19" t="s">
         <v>594</v>
@@ -61776,7 +61764,7 @@
         <v>419</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E148" s="48" t="s">
         <v>421</v>
@@ -61800,7 +61788,7 @@
         <v>427</v>
       </c>
       <c r="L148" s="21" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="M148" s="48" t="s">
         <v>429</v>
@@ -61844,7 +61832,7 @@
         <v>455</v>
       </c>
       <c r="BL148" s="41" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="BM148" s="56" t="s">
         <v>456</v>
@@ -61862,13 +61850,13 @@
         <v>1654</v>
       </c>
       <c r="CJ148" s="59" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="CK148" s="60" t="s">
         <v>1656</v>
       </c>
       <c r="CL148" s="59" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="CM148" s="60" t="s">
         <v>1657</v>
@@ -61889,25 +61877,25 @@
         <v>618</v>
       </c>
       <c r="CT148" s="70" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="CU148" s="71" t="s">
         <v>620</v>
       </c>
       <c r="CV148" s="70" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="CW148" s="71" t="s">
         <v>622</v>
       </c>
       <c r="CX148" s="70" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="CY148" s="71" t="s">
         <v>624</v>
       </c>
       <c r="CZ148" s="70" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="DA148" s="71" t="s">
         <v>626</v>
@@ -61924,7 +61912,7 @@
         <v>456</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E149" s="48" t="s">
         <v>458</v>
@@ -61948,7 +61936,7 @@
         <v>461</v>
       </c>
       <c r="L149" s="21" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="M149" s="48" t="s">
         <v>463</v>
@@ -61977,7 +61965,7 @@
         <v>482</v>
       </c>
       <c r="BF149" s="41" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="BG149" s="56" t="s">
         <v>484</v>
@@ -61992,7 +61980,7 @@
         <v>482</v>
       </c>
       <c r="BL149" s="41" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="BM149" s="56" t="s">
         <v>484</v>
@@ -62016,19 +62004,19 @@
         <v>1671</v>
       </c>
       <c r="CL149" s="59" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="CM149" s="60" t="s">
         <v>1673</v>
       </c>
       <c r="CN149" s="59" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="CO149" s="73" t="s">
         <v>1675</v>
       </c>
       <c r="CP149" s="59" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="CQ149" s="73" t="s">
         <v>1677</v>
@@ -62037,25 +62025,25 @@
         <v>642</v>
       </c>
       <c r="CT149" s="70" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="CU149" s="71" t="s">
         <v>644</v>
       </c>
       <c r="CV149" s="70" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="CW149" s="71" t="s">
         <v>646</v>
       </c>
       <c r="CX149" s="70" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="CY149" s="71" t="s">
         <v>648</v>
       </c>
       <c r="CZ149" s="70" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="DA149" s="71" t="s">
         <v>650</v>
@@ -62072,7 +62060,7 @@
         <v>484</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="E150" s="48" t="s">
         <v>486</v>
@@ -62084,7 +62072,7 @@
         <v>488</v>
       </c>
       <c r="H150" s="37" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="I150" s="49" t="s">
         <v>490</v>
@@ -62096,7 +62084,7 @@
         <v>491</v>
       </c>
       <c r="L150" s="21" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="M150" s="48" t="s">
         <v>492</v>
@@ -62125,7 +62113,7 @@
         <v>519</v>
       </c>
       <c r="BF150" s="41" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="BG150" s="56" t="s">
         <v>521</v>
@@ -62140,7 +62128,7 @@
         <v>519</v>
       </c>
       <c r="BL150" s="41" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="BM150" s="56" t="s">
         <v>521</v>
@@ -62158,25 +62146,25 @@
         <v>652</v>
       </c>
       <c r="CT150" s="70" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="CU150" s="71" t="s">
         <v>654</v>
       </c>
       <c r="CV150" s="70" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="CW150" s="71" t="s">
         <v>656</v>
       </c>
       <c r="CX150" s="70" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="CY150" s="71" t="s">
         <v>658</v>
       </c>
       <c r="CZ150" s="70" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="DA150" s="71" t="s">
         <v>660</v>
@@ -62193,7 +62181,7 @@
         <v>521</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E151" s="48" t="s">
         <v>523</v>
@@ -62205,7 +62193,7 @@
         <v>524</v>
       </c>
       <c r="H151" s="37" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I151" s="49" t="s">
         <v>526</v>
@@ -62217,7 +62205,7 @@
         <v>527</v>
       </c>
       <c r="L151" s="21" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="M151" s="48" t="s">
         <v>528</v>
@@ -62246,7 +62234,7 @@
         <v>549</v>
       </c>
       <c r="BF151" s="41" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="BG151" s="56" t="s">
         <v>551</v>
@@ -62261,7 +62249,7 @@
         <v>549</v>
       </c>
       <c r="BL151" s="41" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="BM151" s="56" t="s">
         <v>551</v>
@@ -62279,25 +62267,25 @@
         <v>664</v>
       </c>
       <c r="CT151" s="46" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="CU151" s="19" t="s">
         <v>666</v>
       </c>
       <c r="CV151" s="46" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="CW151" s="19" t="s">
         <v>668</v>
       </c>
       <c r="CX151" s="46" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="CY151" s="19" t="s">
         <v>670</v>
       </c>
       <c r="CZ151" s="46" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="DA151" s="19" t="s">
         <v>672</v>
@@ -62308,13 +62296,13 @@
         <v>549</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="C152" s="48" t="s">
         <v>551</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="E152" s="48" t="s">
         <v>552</v>
@@ -62326,19 +62314,19 @@
         <v>553</v>
       </c>
       <c r="H152" s="37" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="I152" s="49" t="s">
         <v>554</v>
       </c>
       <c r="J152" s="21" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K152" s="48" t="s">
         <v>556</v>
       </c>
       <c r="L152" s="21" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="M152" s="48" t="s">
         <v>557</v>
@@ -62367,7 +62355,7 @@
         <v>576</v>
       </c>
       <c r="BF152" s="41" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="BG152" s="56" t="s">
         <v>578</v>
@@ -62382,7 +62370,7 @@
         <v>576</v>
       </c>
       <c r="BL152" s="41" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="BM152" s="56" t="s">
         <v>578</v>
@@ -62400,25 +62388,25 @@
         <v>691</v>
       </c>
       <c r="CT152" s="46" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="CU152" s="19" t="s">
         <v>693</v>
       </c>
       <c r="CV152" s="46" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="CW152" s="19" t="s">
         <v>695</v>
       </c>
       <c r="CX152" s="46" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="CY152" s="19" t="s">
         <v>697</v>
       </c>
       <c r="CZ152" s="46" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="DA152" s="19" t="s">
         <v>699</v>
@@ -62435,7 +62423,7 @@
         <v>578</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="E153" s="48" t="s">
         <v>579</v>
@@ -62447,7 +62435,7 @@
         <v>580</v>
       </c>
       <c r="H153" s="37" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I153" s="49" t="s">
         <v>581</v>
@@ -62459,7 +62447,7 @@
         <v>582</v>
       </c>
       <c r="L153" s="21" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="M153" s="48" t="s">
         <v>583</v>
@@ -62503,7 +62491,7 @@
         <v>596</v>
       </c>
       <c r="BL153" s="41" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="BM153" s="56" t="s">
         <v>598</v>
@@ -62521,25 +62509,25 @@
         <v>724</v>
       </c>
       <c r="CT153" s="46" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="CU153" s="19" t="s">
         <v>726</v>
       </c>
       <c r="CV153" s="46" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="CW153" s="19" t="s">
         <v>728</v>
       </c>
       <c r="CX153" s="46" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="CY153" s="19" t="s">
         <v>730</v>
       </c>
       <c r="CZ153" s="46" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="DA153" s="19" t="s">
         <v>732</v>
@@ -62556,7 +62544,7 @@
         <v>598</v>
       </c>
       <c r="D154" s="21" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="E154" s="48" t="s">
         <v>600</v>
@@ -62568,7 +62556,7 @@
         <v>602</v>
       </c>
       <c r="H154" s="37" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="I154" s="49" t="s">
         <v>604</v>
@@ -62580,7 +62568,7 @@
         <v>605</v>
       </c>
       <c r="L154" s="21" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="M154" s="48" t="s">
         <v>606</v>
@@ -62880,13 +62868,13 @@
         <v>673</v>
       </c>
       <c r="CT158" s="70" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="CU158" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV158" s="70" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="CW158" s="71" t="s">
         <v>677</v>
@@ -62897,37 +62885,37 @@
         <v>417</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="C159" s="48" t="s">
         <v>419</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="E159" s="48" t="s">
         <v>421</v>
       </c>
       <c r="F159" s="37" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="G159" s="49" t="s">
         <v>423</v>
       </c>
       <c r="H159" s="37" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="I159" s="49" t="s">
         <v>425</v>
       </c>
       <c r="J159" s="21" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="K159" s="48" t="s">
         <v>427</v>
       </c>
       <c r="L159" s="21" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="M159" s="48" t="s">
         <v>429</v>
@@ -62956,13 +62944,13 @@
         <v>417</v>
       </c>
       <c r="BF159" s="41" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="BG159" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH159" s="41" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="BI159" s="56" t="s">
         <v>421</v>
@@ -62977,13 +62965,13 @@
         <v>700</v>
       </c>
       <c r="CT159" s="70" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="CU159" s="71" t="s">
         <v>701</v>
       </c>
       <c r="CV159" s="70" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="CW159" s="71" t="s">
         <v>703</v>
@@ -62994,37 +62982,37 @@
         <v>455</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C160" s="48" t="s">
         <v>456</v>
       </c>
       <c r="D160" s="21" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="E160" s="48" t="s">
         <v>458</v>
       </c>
       <c r="F160" s="37" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="G160" s="49" t="s">
         <v>459</v>
       </c>
       <c r="H160" s="37" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="I160" s="49" t="s">
         <v>460</v>
       </c>
       <c r="J160" s="21" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="K160" s="48" t="s">
         <v>461</v>
       </c>
       <c r="L160" s="21" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="M160" s="48" t="s">
         <v>463</v>
@@ -63053,7 +63041,7 @@
         <v>455</v>
       </c>
       <c r="BF160" s="41" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="BG160" s="56" t="s">
         <v>456</v>
@@ -63074,13 +63062,13 @@
         <v>733</v>
       </c>
       <c r="CT160" s="70" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="CU160" s="71" t="s">
         <v>735</v>
       </c>
       <c r="CV160" s="70" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="CW160" s="71" t="s">
         <v>737</v>
@@ -63091,37 +63079,37 @@
         <v>482</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C161" s="48" t="s">
         <v>484</v>
       </c>
       <c r="D161" s="21" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E161" s="48" t="s">
         <v>486</v>
       </c>
       <c r="F161" s="37" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G161" s="49" t="s">
         <v>488</v>
       </c>
       <c r="H161" s="37" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="I161" s="49" t="s">
         <v>490</v>
       </c>
       <c r="J161" s="21" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="K161" s="48" t="s">
         <v>491</v>
       </c>
       <c r="L161" s="21" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="M161" s="48" t="s">
         <v>492</v>
@@ -63178,37 +63166,37 @@
         <v>519</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C162" s="48" t="s">
         <v>521</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E162" s="48" t="s">
         <v>523</v>
       </c>
       <c r="F162" s="37" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="G162" s="49" t="s">
         <v>524</v>
       </c>
       <c r="H162" s="37" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="I162" s="49" t="s">
         <v>526</v>
       </c>
       <c r="J162" s="21" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="K162" s="48" t="s">
         <v>527</v>
       </c>
       <c r="L162" s="21" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="M162" s="48" t="s">
         <v>528</v>
@@ -63243,7 +63231,7 @@
         <v>521</v>
       </c>
       <c r="BH162" s="41" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="BI162" s="56" t="s">
         <v>523</v>
@@ -63260,37 +63248,37 @@
         <v>549</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C163" s="48" t="s">
         <v>551</v>
       </c>
       <c r="D163" s="21" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E163" s="48" t="s">
         <v>552</v>
       </c>
       <c r="F163" s="37" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G163" s="49" t="s">
         <v>553</v>
       </c>
       <c r="H163" s="37" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="I163" s="49" t="s">
         <v>554</v>
       </c>
       <c r="J163" s="21" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="K163" s="48" t="s">
         <v>556</v>
       </c>
       <c r="L163" s="21" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="M163" s="48" t="s">
         <v>557</v>
@@ -63319,7 +63307,7 @@
         <v>549</v>
       </c>
       <c r="BF163" s="41" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="BG163" s="56" t="s">
         <v>551</v>
@@ -63361,37 +63349,37 @@
         <v>576</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C164" s="48" t="s">
         <v>578</v>
       </c>
       <c r="D164" s="21" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E164" s="48" t="s">
         <v>579</v>
       </c>
       <c r="F164" s="37" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="G164" s="49" t="s">
         <v>580</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="I164" s="49" t="s">
         <v>581</v>
       </c>
       <c r="J164" s="21" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="K164" s="48" t="s">
         <v>582</v>
       </c>
       <c r="L164" s="21" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="M164" s="48" t="s">
         <v>583</v>
@@ -63426,7 +63414,7 @@
         <v>578</v>
       </c>
       <c r="BH164" s="41" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="BI164" s="56" t="s">
         <v>579</v>
@@ -63462,37 +63450,37 @@
         <v>596</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C165" s="48" t="s">
         <v>598</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="E165" s="48" t="s">
         <v>600</v>
       </c>
       <c r="F165" s="37" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="G165" s="49" t="s">
         <v>602</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="I165" s="49" t="s">
         <v>604</v>
       </c>
       <c r="J165" s="21" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="K165" s="48" t="s">
         <v>605</v>
       </c>
       <c r="L165" s="21" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="M165" s="48" t="s">
         <v>606</v>
@@ -63521,7 +63509,7 @@
         <v>596</v>
       </c>
       <c r="BF165" s="41" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="BG165" s="56" t="s">
         <v>598</v>
@@ -63563,7 +63551,7 @@
         <v>636</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C166" s="48" t="s">
         <v>636</v>
@@ -63608,7 +63596,7 @@
         <v>629</v>
       </c>
       <c r="BH166" s="41" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="BI166" s="56" t="s">
         <v>630</v>
@@ -63770,13 +63758,13 @@
         <v>570</v>
       </c>
       <c r="CX168" s="46" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="CY168" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CZ168" s="46" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="DA168" s="19" t="s">
         <v>574</v>
@@ -63869,7 +63857,7 @@
         <v>592</v>
       </c>
       <c r="CZ169" s="46" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="DA169" s="19" t="s">
         <v>594</v>
@@ -63939,13 +63927,13 @@
         <v>417</v>
       </c>
       <c r="BF170" s="41" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="BG170" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH170" s="41" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="BI170" s="56" t="s">
         <v>421</v>
@@ -63960,7 +63948,7 @@
         <v>618</v>
       </c>
       <c r="CT170" s="70" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="CU170" s="71" t="s">
         <v>620</v>
@@ -64048,13 +64036,13 @@
         <v>455</v>
       </c>
       <c r="BF171" s="41" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="BG171" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH171" s="41" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="BI171" s="56" t="s">
         <v>458</v>
@@ -64069,19 +64057,19 @@
         <v>642</v>
       </c>
       <c r="CT171" s="70" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="CU171" s="71" t="s">
         <v>644</v>
       </c>
       <c r="CV171" s="70" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="CW171" s="71" t="s">
         <v>646</v>
       </c>
       <c r="CX171" s="70" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="CY171" s="71" t="s">
         <v>648</v>
@@ -64098,7 +64086,7 @@
         <v>482</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C172" s="48" t="s">
         <v>484</v>
@@ -64122,7 +64110,7 @@
         <v>490</v>
       </c>
       <c r="J172" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K172" s="48" t="s">
         <v>491</v>
@@ -64157,13 +64145,13 @@
         <v>482</v>
       </c>
       <c r="BF172" s="41" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="BG172" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH172" s="41" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="BI172" s="56" t="s">
         <v>486</v>
@@ -64178,13 +64166,13 @@
         <v>652</v>
       </c>
       <c r="CT172" s="70" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="CU172" s="71" t="s">
         <v>654</v>
       </c>
       <c r="CV172" s="70" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="CW172" s="71" t="s">
         <v>656</v>
@@ -64266,13 +64254,13 @@
         <v>519</v>
       </c>
       <c r="BF173" s="41" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="BG173" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH173" s="41" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="BI173" s="56" t="s">
         <v>523</v>
@@ -64287,25 +64275,25 @@
         <v>664</v>
       </c>
       <c r="CT173" s="46" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="CU173" s="19" t="s">
         <v>666</v>
       </c>
       <c r="CV173" s="46" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="CW173" s="19" t="s">
         <v>668</v>
       </c>
       <c r="CX173" s="46" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="CY173" s="19" t="s">
         <v>670</v>
       </c>
       <c r="CZ173" s="46" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="DA173" s="19" t="s">
         <v>672</v>
@@ -64375,13 +64363,13 @@
         <v>549</v>
       </c>
       <c r="BF174" s="41" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="BG174" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH174" s="41" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="BI174" s="56" t="s">
         <v>552</v>
@@ -64396,25 +64384,25 @@
         <v>691</v>
       </c>
       <c r="CT174" s="46" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="CU174" s="19" t="s">
         <v>693</v>
       </c>
       <c r="CV174" s="46" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="CW174" s="19" t="s">
         <v>695</v>
       </c>
       <c r="CX174" s="46" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="CY174" s="19" t="s">
         <v>697</v>
       </c>
       <c r="CZ174" s="46" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="DA174" s="19" t="s">
         <v>699</v>
@@ -64484,13 +64472,13 @@
         <v>576</v>
       </c>
       <c r="BF175" s="41" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="BG175" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH175" s="41" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="BI175" s="56" t="s">
         <v>579</v>
@@ -64505,25 +64493,25 @@
         <v>724</v>
       </c>
       <c r="CT175" s="46" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="CU175" s="19" t="s">
         <v>726</v>
       </c>
       <c r="CV175" s="46" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="CW175" s="19" t="s">
         <v>728</v>
       </c>
       <c r="CX175" s="46" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="CY175" s="19" t="s">
         <v>730</v>
       </c>
       <c r="CZ175" s="46" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="DA175" s="19" t="s">
         <v>732</v>
@@ -64593,13 +64581,13 @@
         <v>596</v>
       </c>
       <c r="BF176" s="41" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="BG176" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH176" s="41" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="BI176" s="56" t="s">
         <v>600</v>
@@ -64625,7 +64613,7 @@
         <v>627</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C177" s="48" t="s">
         <v>629</v>
@@ -64684,13 +64672,13 @@
         <v>627</v>
       </c>
       <c r="BF177" s="41" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="BG177" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH177" s="41" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="BI177" s="56" t="s">
         <v>630</v>
@@ -64746,7 +64734,7 @@
         <v>636</v>
       </c>
       <c r="BF178" s="41" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="BG178" s="56" t="s">
         <v>636</v>
@@ -64811,13 +64799,13 @@
         <v>673</v>
       </c>
       <c r="CT179" s="70" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="CU179" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV179" s="70" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="CW179" s="71" t="s">
         <v>677</v>
@@ -64896,7 +64884,7 @@
         <v>701</v>
       </c>
       <c r="CV180" s="70" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="CW180" s="71" t="s">
         <v>703</v>
@@ -64987,7 +64975,7 @@
         <v>733</v>
       </c>
       <c r="CT181" s="70" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="CU181" s="71" t="s">
         <v>735</v>
@@ -65089,7 +65077,7 @@
         <v>482</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C183" s="48" t="s">
         <v>484</v>
@@ -65113,7 +65101,7 @@
         <v>490</v>
       </c>
       <c r="J183" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K183" s="48" t="s">
         <v>491</v>
@@ -65148,7 +65136,7 @@
         <v>482</v>
       </c>
       <c r="BF183" s="41" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="BG183" s="56" t="s">
         <v>484</v>
@@ -65230,7 +65218,7 @@
         <v>519</v>
       </c>
       <c r="BF184" s="41" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="BG184" s="56" t="s">
         <v>521</v>
@@ -65331,7 +65319,7 @@
         <v>549</v>
       </c>
       <c r="BF185" s="41" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="BG185" s="56" t="s">
         <v>551</v>
@@ -65357,13 +65345,13 @@
         <v>618</v>
       </c>
       <c r="CT185" s="62" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="CU185" s="63" t="s">
         <v>620</v>
       </c>
       <c r="CV185" s="62" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="CW185" s="63" t="s">
         <v>622</v>
@@ -65443,7 +65431,7 @@
         <v>576</v>
       </c>
       <c r="BF186" s="41" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="BG186" s="56" t="s">
         <v>578</v>
@@ -65469,7 +65457,7 @@
         <v>642</v>
       </c>
       <c r="CT186" s="62" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="CU186" s="63" t="s">
         <v>644</v>
@@ -65512,7 +65500,7 @@
         <v>602</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="I187" s="49" t="s">
         <v>604</v>
@@ -65553,7 +65541,7 @@
         <v>596</v>
       </c>
       <c r="BF187" s="41" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="BG187" s="56" t="s">
         <v>598</v>
@@ -65579,13 +65567,13 @@
         <v>652</v>
       </c>
       <c r="CT187" s="62" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="CU187" s="63" t="s">
         <v>654</v>
       </c>
       <c r="CV187" s="62" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="CW187" s="63" t="s">
         <v>656</v>
@@ -65663,13 +65651,13 @@
         <v>627</v>
       </c>
       <c r="BF188" s="41" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="BG188" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH188" s="41" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="BI188" s="56" t="s">
         <v>630</v>
@@ -65739,7 +65727,7 @@
         <v>636</v>
       </c>
       <c r="BF189" s="41" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="BG189" s="56" t="s">
         <v>636</v>
@@ -65902,25 +65890,25 @@
         <v>443</v>
       </c>
       <c r="CT191" s="70" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="CU191" s="71" t="s">
         <v>445</v>
       </c>
       <c r="CV191" s="70" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="CW191" s="71" t="s">
         <v>447</v>
       </c>
       <c r="CX191" s="70" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="CY191" s="71" t="s">
         <v>449</v>
       </c>
       <c r="CZ191" s="70" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="DA191" s="71" t="s">
         <v>451</v>
@@ -65990,7 +65978,7 @@
         <v>417</v>
       </c>
       <c r="BF192" s="41" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="BG192" s="56" t="s">
         <v>419</v>
@@ -66014,25 +66002,25 @@
         <v>470</v>
       </c>
       <c r="CT192" s="70" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="CU192" s="71" t="s">
         <v>472</v>
       </c>
       <c r="CV192" s="70" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="CW192" s="71" t="s">
         <v>474</v>
       </c>
       <c r="CX192" s="70" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="CY192" s="71" t="s">
         <v>476</v>
       </c>
       <c r="CZ192" s="70" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="DA192" s="71" t="s">
         <v>478</v>
@@ -66102,7 +66090,7 @@
         <v>455</v>
       </c>
       <c r="BF193" s="41" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="BG193" s="56" t="s">
         <v>456</v>
@@ -66126,25 +66114,25 @@
         <v>507</v>
       </c>
       <c r="CT193" s="70" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="CU193" s="71" t="s">
         <v>509</v>
       </c>
       <c r="CV193" s="70" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="CW193" s="71" t="s">
         <v>511</v>
       </c>
       <c r="CX193" s="70" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="CY193" s="71" t="s">
         <v>512</v>
       </c>
       <c r="CZ193" s="70" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="DA193" s="71" t="s">
         <v>514</v>
@@ -66155,7 +66143,7 @@
         <v>482</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C194" s="48" t="s">
         <v>484</v>
@@ -66179,7 +66167,7 @@
         <v>490</v>
       </c>
       <c r="J194" s="21" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K194" s="48" t="s">
         <v>491</v>
@@ -66236,25 +66224,25 @@
         <v>538</v>
       </c>
       <c r="CT194" s="46" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="CU194" s="19" t="s">
         <v>540</v>
       </c>
       <c r="CV194" s="46" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="CW194" s="19" t="s">
         <v>542</v>
       </c>
       <c r="CX194" s="46" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="CY194" s="19" t="s">
         <v>544</v>
       </c>
       <c r="CZ194" s="46" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="DA194" s="19" t="s">
         <v>546</v>
@@ -66346,25 +66334,25 @@
         <v>567</v>
       </c>
       <c r="CT195" s="46" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="CU195" s="19" t="s">
         <v>569</v>
       </c>
       <c r="CV195" s="46" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="CW195" s="19" t="s">
         <v>570</v>
       </c>
       <c r="CX195" s="46" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="CY195" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CZ195" s="46" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="DA195" s="19" t="s">
         <v>574</v>
@@ -66456,25 +66444,25 @@
         <v>589</v>
       </c>
       <c r="CT196" s="46" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="CU196" s="19" t="s">
         <v>590</v>
       </c>
       <c r="CV196" s="46" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="CW196" s="19" t="s">
         <v>591</v>
       </c>
       <c r="CX196" s="46" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="CY196" s="19" t="s">
         <v>592</v>
       </c>
       <c r="CZ196" s="46" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="DA196" s="19" t="s">
         <v>594</v>
@@ -66566,25 +66554,25 @@
         <v>618</v>
       </c>
       <c r="CT197" s="70" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="CU197" s="71" t="s">
         <v>620</v>
       </c>
       <c r="CV197" s="70" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="CW197" s="71" t="s">
         <v>622</v>
       </c>
       <c r="CX197" s="70" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="CY197" s="71" t="s">
         <v>624</v>
       </c>
       <c r="CZ197" s="70" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="DA197" s="71" t="s">
         <v>626</v>
@@ -66613,7 +66601,7 @@
         <v>602</v>
       </c>
       <c r="H198" s="37" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="I198" s="49" t="s">
         <v>604</v>
@@ -66676,25 +66664,25 @@
         <v>642</v>
       </c>
       <c r="CT198" s="70" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="CU198" s="71" t="s">
         <v>644</v>
       </c>
       <c r="CV198" s="70" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="CW198" s="71" t="s">
         <v>646</v>
       </c>
       <c r="CX198" s="70" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="CY198" s="71" t="s">
         <v>648</v>
       </c>
       <c r="CZ198" s="70" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="DA198" s="71" t="s">
         <v>650</v>
@@ -66786,25 +66774,25 @@
         <v>652</v>
       </c>
       <c r="CT199" s="70" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="CU199" s="71" t="s">
         <v>654</v>
       </c>
       <c r="CV199" s="70" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="CW199" s="71" t="s">
         <v>656</v>
       </c>
       <c r="CX199" s="70" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="CY199" s="71" t="s">
         <v>658</v>
       </c>
       <c r="CZ199" s="70" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="DA199" s="71" t="s">
         <v>660</v>
@@ -66985,28 +66973,28 @@
         <v>673</v>
       </c>
       <c r="CT202" s="70" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="CU202" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV202" s="70" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="CW202" s="71" t="s">
         <v>677</v>
       </c>
       <c r="CX202" s="70" t="s">
+        <v>2022</v>
+      </c>
+      <c r="CY202" s="71" t="s">
+        <v>946</v>
+      </c>
+      <c r="CZ202" s="70" t="s">
         <v>2023</v>
       </c>
-      <c r="CY202" s="71" t="s">
-        <v>945</v>
-      </c>
-      <c r="CZ202" s="70" t="s">
-        <v>2024</v>
-      </c>
       <c r="DA202" s="71" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -67066,28 +67054,28 @@
         <v>700</v>
       </c>
       <c r="CT203" s="70" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="CU203" s="71" t="s">
         <v>701</v>
       </c>
       <c r="CV203" s="70" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="CW203" s="71" t="s">
         <v>703</v>
       </c>
       <c r="CX203" s="70" t="s">
+        <v>2026</v>
+      </c>
+      <c r="CY203" s="71" t="s">
+        <v>960</v>
+      </c>
+      <c r="CZ203" s="70" t="s">
         <v>2027</v>
       </c>
-      <c r="CY203" s="71" t="s">
-        <v>959</v>
-      </c>
-      <c r="CZ203" s="70" t="s">
-        <v>2028</v>
-      </c>
       <c r="DA203" s="71" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="54.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67147,28 +67135,28 @@
         <v>733</v>
       </c>
       <c r="CT204" s="70" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="CU204" s="71" t="s">
         <v>735</v>
       </c>
       <c r="CV204" s="70" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="CW204" s="71" t="s">
         <v>737</v>
       </c>
       <c r="CX204" s="70" t="s">
+        <v>2030</v>
+      </c>
+      <c r="CY204" s="71" t="s">
+        <v>975</v>
+      </c>
+      <c r="CZ204" s="70" t="s">
         <v>2031</v>
       </c>
-      <c r="CY204" s="71" t="s">
-        <v>974</v>
-      </c>
-      <c r="CZ204" s="70" t="s">
-        <v>2032</v>
-      </c>
       <c r="DA204" s="71" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -67202,7 +67190,7 @@
         <v>482</v>
       </c>
       <c r="BF205" s="41" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="BG205" s="56" t="s">
         <v>484</v>
@@ -67271,7 +67259,7 @@
         <v>521</v>
       </c>
       <c r="BH206" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BI206" s="56" t="s">
         <v>523</v>
@@ -67328,7 +67316,7 @@
         <v>549</v>
       </c>
       <c r="BF207" s="41" t="s">
-        <v>1231</v>
+        <v>2032</v>
       </c>
       <c r="BG207" s="56" t="s">
         <v>551</v>
@@ -67397,7 +67385,7 @@
         <v>578</v>
       </c>
       <c r="BH208" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BI208" s="56" t="s">
         <v>579</v>
@@ -67460,7 +67448,7 @@
         <v>598</v>
       </c>
       <c r="BH209" s="41" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="BI209" s="56" t="s">
         <v>600</v>
@@ -69420,7 +69408,7 @@
         <v>482</v>
       </c>
       <c r="BF249" s="41" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="BG249" s="56" t="s">
         <v>484</v>
@@ -70682,7 +70670,7 @@
         <v>419</v>
       </c>
       <c r="BH280" s="41" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="BI280" s="56" t="s">
         <v>421</v>
@@ -70708,13 +70696,13 @@
         <v>455</v>
       </c>
       <c r="BF281" s="41" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="BG281" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH281" s="41" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="BI281" s="56" t="s">
         <v>458</v>
@@ -70740,7 +70728,7 @@
         <v>482</v>
       </c>
       <c r="BF282" s="41" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="BG282" s="56" t="s">
         <v>484</v>
@@ -70778,7 +70766,7 @@
         <v>521</v>
       </c>
       <c r="BH283" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BI283" s="56" t="s">
         <v>523</v>
@@ -70798,7 +70786,7 @@
         <v>549</v>
       </c>
       <c r="BF284" s="41" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="BG284" s="56" t="s">
         <v>551</v>
@@ -70824,7 +70812,7 @@
         <v>578</v>
       </c>
       <c r="BH285" s="41" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="BI285" s="56" t="s">
         <v>579</v>
@@ -70864,7 +70852,7 @@
         <v>629</v>
       </c>
       <c r="BH287" s="41" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="BI287" s="56" t="s">
         <v>630</v>

--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9962" uniqueCount="2678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9966" uniqueCount="2679">
   <si>
     <t xml:space="preserve">inflection name</t>
   </si>
@@ -6842,6 +6842,9 @@
 santamhā
 santasmā
 santā</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ete</t>
   </si>
   <si>
     <t xml:space="preserve">ubhayamhi
@@ -63440,47 +63443,55 @@
       <c r="CW164" s="71" t="s">
         <v>447</v>
       </c>
-      <c r="CX164" s="70"/>
-      <c r="CY164" s="71"/>
-      <c r="CZ164" s="70"/>
-      <c r="DA164" s="71"/>
+      <c r="CX164" s="70" t="s">
+        <v>1933</v>
+      </c>
+      <c r="CY164" s="71" t="s">
+        <v>449</v>
+      </c>
+      <c r="CZ164" s="70" t="s">
+        <v>860</v>
+      </c>
+      <c r="DA164" s="71" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="21" t="s">
         <v>596</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C165" s="48" t="s">
         <v>598</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="E165" s="48" t="s">
         <v>600</v>
       </c>
       <c r="F165" s="37" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G165" s="49" t="s">
         <v>602</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="I165" s="49" t="s">
         <v>604</v>
       </c>
       <c r="J165" s="21" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="K165" s="48" t="s">
         <v>605</v>
       </c>
       <c r="L165" s="21" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="M165" s="48" t="s">
         <v>606</v>
@@ -63509,7 +63520,7 @@
         <v>596</v>
       </c>
       <c r="BF165" s="41" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="BG165" s="56" t="s">
         <v>598</v>
@@ -63551,7 +63562,7 @@
         <v>636</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="C166" s="48" t="s">
         <v>636</v>
@@ -63758,13 +63769,13 @@
         <v>570</v>
       </c>
       <c r="CX168" s="46" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="CY168" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CZ168" s="46" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="DA168" s="19" t="s">
         <v>574</v>
@@ -63857,7 +63868,7 @@
         <v>592</v>
       </c>
       <c r="CZ169" s="46" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="DA169" s="19" t="s">
         <v>594</v>
@@ -63927,13 +63938,13 @@
         <v>417</v>
       </c>
       <c r="BF170" s="41" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="BG170" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH170" s="41" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="BI170" s="56" t="s">
         <v>421</v>
@@ -63948,7 +63959,7 @@
         <v>618</v>
       </c>
       <c r="CT170" s="70" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="CU170" s="71" t="s">
         <v>620</v>
@@ -64036,13 +64047,13 @@
         <v>455</v>
       </c>
       <c r="BF171" s="41" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="BG171" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH171" s="41" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="BI171" s="56" t="s">
         <v>458</v>
@@ -64057,13 +64068,13 @@
         <v>642</v>
       </c>
       <c r="CT171" s="70" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="CU171" s="71" t="s">
         <v>644</v>
       </c>
       <c r="CV171" s="70" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="CW171" s="71" t="s">
         <v>646</v>
@@ -64145,13 +64156,13 @@
         <v>482</v>
       </c>
       <c r="BF172" s="41" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="BG172" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH172" s="41" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="BI172" s="56" t="s">
         <v>486</v>
@@ -64166,13 +64177,13 @@
         <v>652</v>
       </c>
       <c r="CT172" s="70" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="CU172" s="71" t="s">
         <v>654</v>
       </c>
       <c r="CV172" s="70" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="CW172" s="71" t="s">
         <v>656</v>
@@ -64254,13 +64265,13 @@
         <v>519</v>
       </c>
       <c r="BF173" s="41" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="BG173" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH173" s="41" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="BI173" s="56" t="s">
         <v>523</v>
@@ -64275,25 +64286,25 @@
         <v>664</v>
       </c>
       <c r="CT173" s="46" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="CU173" s="19" t="s">
         <v>666</v>
       </c>
       <c r="CV173" s="46" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="CW173" s="19" t="s">
         <v>668</v>
       </c>
       <c r="CX173" s="46" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="CY173" s="19" t="s">
         <v>670</v>
       </c>
       <c r="CZ173" s="46" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="DA173" s="19" t="s">
         <v>672</v>
@@ -64363,13 +64374,13 @@
         <v>549</v>
       </c>
       <c r="BF174" s="41" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="BG174" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH174" s="41" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="BI174" s="56" t="s">
         <v>552</v>
@@ -64384,25 +64395,25 @@
         <v>691</v>
       </c>
       <c r="CT174" s="46" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="CU174" s="19" t="s">
         <v>693</v>
       </c>
       <c r="CV174" s="46" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="CW174" s="19" t="s">
         <v>695</v>
       </c>
       <c r="CX174" s="46" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="CY174" s="19" t="s">
         <v>697</v>
       </c>
       <c r="CZ174" s="46" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="DA174" s="19" t="s">
         <v>699</v>
@@ -64472,13 +64483,13 @@
         <v>576</v>
       </c>
       <c r="BF175" s="41" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="BG175" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH175" s="41" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="BI175" s="56" t="s">
         <v>579</v>
@@ -64493,25 +64504,25 @@
         <v>724</v>
       </c>
       <c r="CT175" s="46" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="CU175" s="19" t="s">
         <v>726</v>
       </c>
       <c r="CV175" s="46" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="CW175" s="19" t="s">
         <v>728</v>
       </c>
       <c r="CX175" s="46" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="CY175" s="19" t="s">
         <v>730</v>
       </c>
       <c r="CZ175" s="46" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="DA175" s="19" t="s">
         <v>732</v>
@@ -64581,13 +64592,13 @@
         <v>596</v>
       </c>
       <c r="BF176" s="41" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="BG176" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH176" s="41" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="BI176" s="56" t="s">
         <v>600</v>
@@ -64672,13 +64683,13 @@
         <v>627</v>
       </c>
       <c r="BF177" s="41" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="BG177" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH177" s="41" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="BI177" s="56" t="s">
         <v>630</v>
@@ -64734,7 +64745,7 @@
         <v>636</v>
       </c>
       <c r="BF178" s="41" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="BG178" s="56" t="s">
         <v>636</v>
@@ -64799,13 +64810,13 @@
         <v>673</v>
       </c>
       <c r="CT179" s="70" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="CU179" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV179" s="70" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="CW179" s="71" t="s">
         <v>677</v>
@@ -64884,7 +64895,7 @@
         <v>701</v>
       </c>
       <c r="CV180" s="70" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="CW180" s="71" t="s">
         <v>703</v>
@@ -64975,7 +64986,7 @@
         <v>733</v>
       </c>
       <c r="CT181" s="70" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="CU181" s="71" t="s">
         <v>735</v>
@@ -65136,7 +65147,7 @@
         <v>482</v>
       </c>
       <c r="BF183" s="41" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="BG183" s="56" t="s">
         <v>484</v>
@@ -65218,7 +65229,7 @@
         <v>519</v>
       </c>
       <c r="BF184" s="41" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="BG184" s="56" t="s">
         <v>521</v>
@@ -65319,7 +65330,7 @@
         <v>549</v>
       </c>
       <c r="BF185" s="41" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="BG185" s="56" t="s">
         <v>551</v>
@@ -65345,13 +65356,13 @@
         <v>618</v>
       </c>
       <c r="CT185" s="62" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="CU185" s="63" t="s">
         <v>620</v>
       </c>
       <c r="CV185" s="62" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="CW185" s="63" t="s">
         <v>622</v>
@@ -65431,7 +65442,7 @@
         <v>576</v>
       </c>
       <c r="BF186" s="41" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="BG186" s="56" t="s">
         <v>578</v>
@@ -65457,7 +65468,7 @@
         <v>642</v>
       </c>
       <c r="CT186" s="62" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="CU186" s="63" t="s">
         <v>644</v>
@@ -65541,7 +65552,7 @@
         <v>596</v>
       </c>
       <c r="BF187" s="41" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="BG187" s="56" t="s">
         <v>598</v>
@@ -65567,13 +65578,13 @@
         <v>652</v>
       </c>
       <c r="CT187" s="62" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="CU187" s="63" t="s">
         <v>654</v>
       </c>
       <c r="CV187" s="62" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="CW187" s="63" t="s">
         <v>656</v>
@@ -65651,13 +65662,13 @@
         <v>627</v>
       </c>
       <c r="BF188" s="41" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="BG188" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH188" s="41" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="BI188" s="56" t="s">
         <v>630</v>
@@ -65727,7 +65738,7 @@
         <v>636</v>
       </c>
       <c r="BF189" s="41" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="BG189" s="56" t="s">
         <v>636</v>
@@ -65890,25 +65901,25 @@
         <v>443</v>
       </c>
       <c r="CT191" s="70" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="CU191" s="71" t="s">
         <v>445</v>
       </c>
       <c r="CV191" s="70" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="CW191" s="71" t="s">
         <v>447</v>
       </c>
       <c r="CX191" s="70" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="CY191" s="71" t="s">
         <v>449</v>
       </c>
       <c r="CZ191" s="70" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="DA191" s="71" t="s">
         <v>451</v>
@@ -65978,7 +65989,7 @@
         <v>417</v>
       </c>
       <c r="BF192" s="41" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="BG192" s="56" t="s">
         <v>419</v>
@@ -66002,25 +66013,25 @@
         <v>470</v>
       </c>
       <c r="CT192" s="70" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="CU192" s="71" t="s">
         <v>472</v>
       </c>
       <c r="CV192" s="70" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="CW192" s="71" t="s">
         <v>474</v>
       </c>
       <c r="CX192" s="70" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="CY192" s="71" t="s">
         <v>476</v>
       </c>
       <c r="CZ192" s="70" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="DA192" s="71" t="s">
         <v>478</v>
@@ -66090,7 +66101,7 @@
         <v>455</v>
       </c>
       <c r="BF193" s="41" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="BG193" s="56" t="s">
         <v>456</v>
@@ -66114,25 +66125,25 @@
         <v>507</v>
       </c>
       <c r="CT193" s="70" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="CU193" s="71" t="s">
         <v>509</v>
       </c>
       <c r="CV193" s="70" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="CW193" s="71" t="s">
         <v>511</v>
       </c>
       <c r="CX193" s="70" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="CY193" s="71" t="s">
         <v>512</v>
       </c>
       <c r="CZ193" s="70" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="DA193" s="71" t="s">
         <v>514</v>
@@ -66224,25 +66235,25 @@
         <v>538</v>
       </c>
       <c r="CT194" s="46" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="CU194" s="19" t="s">
         <v>540</v>
       </c>
       <c r="CV194" s="46" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="CW194" s="19" t="s">
         <v>542</v>
       </c>
       <c r="CX194" s="46" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="CY194" s="19" t="s">
         <v>544</v>
       </c>
       <c r="CZ194" s="46" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="DA194" s="19" t="s">
         <v>546</v>
@@ -66334,25 +66345,25 @@
         <v>567</v>
       </c>
       <c r="CT195" s="46" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="CU195" s="19" t="s">
         <v>569</v>
       </c>
       <c r="CV195" s="46" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="CW195" s="19" t="s">
         <v>570</v>
       </c>
       <c r="CX195" s="46" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="CY195" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CZ195" s="46" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="DA195" s="19" t="s">
         <v>574</v>
@@ -66444,25 +66455,25 @@
         <v>589</v>
       </c>
       <c r="CT196" s="46" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="CU196" s="19" t="s">
         <v>590</v>
       </c>
       <c r="CV196" s="46" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="CW196" s="19" t="s">
         <v>591</v>
       </c>
       <c r="CX196" s="46" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="CY196" s="19" t="s">
         <v>592</v>
       </c>
       <c r="CZ196" s="46" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="DA196" s="19" t="s">
         <v>594</v>
@@ -66554,25 +66565,25 @@
         <v>618</v>
       </c>
       <c r="CT197" s="70" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="CU197" s="71" t="s">
         <v>620</v>
       </c>
       <c r="CV197" s="70" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="CW197" s="71" t="s">
         <v>622</v>
       </c>
       <c r="CX197" s="70" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="CY197" s="71" t="s">
         <v>624</v>
       </c>
       <c r="CZ197" s="70" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="DA197" s="71" t="s">
         <v>626</v>
@@ -66664,25 +66675,25 @@
         <v>642</v>
       </c>
       <c r="CT198" s="70" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="CU198" s="71" t="s">
         <v>644</v>
       </c>
       <c r="CV198" s="70" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="CW198" s="71" t="s">
         <v>646</v>
       </c>
       <c r="CX198" s="70" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="CY198" s="71" t="s">
         <v>648</v>
       </c>
       <c r="CZ198" s="70" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="DA198" s="71" t="s">
         <v>650</v>
@@ -66774,25 +66785,25 @@
         <v>652</v>
       </c>
       <c r="CT199" s="70" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="CU199" s="71" t="s">
         <v>654</v>
       </c>
       <c r="CV199" s="70" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="CW199" s="71" t="s">
         <v>656</v>
       </c>
       <c r="CX199" s="70" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="CY199" s="71" t="s">
         <v>658</v>
       </c>
       <c r="CZ199" s="70" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="DA199" s="71" t="s">
         <v>660</v>
@@ -66973,25 +66984,25 @@
         <v>673</v>
       </c>
       <c r="CT202" s="70" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="CU202" s="71" t="s">
         <v>675</v>
       </c>
       <c r="CV202" s="70" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="CW202" s="71" t="s">
         <v>677</v>
       </c>
       <c r="CX202" s="70" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="CY202" s="71" t="s">
         <v>946</v>
       </c>
       <c r="CZ202" s="70" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="DA202" s="71" t="s">
         <v>948</v>
@@ -67054,25 +67065,25 @@
         <v>700</v>
       </c>
       <c r="CT203" s="70" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="CU203" s="71" t="s">
         <v>701</v>
       </c>
       <c r="CV203" s="70" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="CW203" s="71" t="s">
         <v>703</v>
       </c>
       <c r="CX203" s="70" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="CY203" s="71" t="s">
         <v>960</v>
       </c>
       <c r="CZ203" s="70" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="DA203" s="71" t="s">
         <v>962</v>
@@ -67135,25 +67146,25 @@
         <v>733</v>
       </c>
       <c r="CT204" s="70" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="CU204" s="71" t="s">
         <v>735</v>
       </c>
       <c r="CV204" s="70" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="CW204" s="71" t="s">
         <v>737</v>
       </c>
       <c r="CX204" s="70" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="CY204" s="71" t="s">
         <v>975</v>
       </c>
       <c r="CZ204" s="70" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="DA204" s="71" t="s">
         <v>977</v>
@@ -67316,7 +67327,7 @@
         <v>549</v>
       </c>
       <c r="BF207" s="41" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="BG207" s="56" t="s">
         <v>551</v>
@@ -67728,13 +67739,13 @@
         <v>417</v>
       </c>
       <c r="BF214" s="41" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="BG214" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH214" s="41" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="BI214" s="56" t="s">
         <v>421</v>
@@ -67782,13 +67793,13 @@
         <v>455</v>
       </c>
       <c r="BF215" s="41" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="BG215" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH215" s="41" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="BI215" s="56" t="s">
         <v>458</v>
@@ -67836,13 +67847,13 @@
         <v>482</v>
       </c>
       <c r="BF216" s="41" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="BG216" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH216" s="41" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="BI216" s="56" t="s">
         <v>486</v>
@@ -67890,13 +67901,13 @@
         <v>519</v>
       </c>
       <c r="BF217" s="41" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="BG217" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH217" s="41" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="BI217" s="56" t="s">
         <v>523</v>
@@ -67944,13 +67955,13 @@
         <v>549</v>
       </c>
       <c r="BF218" s="41" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="BG218" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH218" s="41" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="BI218" s="56" t="s">
         <v>552</v>
@@ -67998,13 +68009,13 @@
         <v>576</v>
       </c>
       <c r="BF219" s="41" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="BG219" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH219" s="41" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="BI219" s="56" t="s">
         <v>579</v>
@@ -68047,13 +68058,13 @@
         <v>596</v>
       </c>
       <c r="BF220" s="41" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="BG220" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH220" s="41" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="BI220" s="56" t="s">
         <v>600</v>
@@ -68096,13 +68107,13 @@
         <v>627</v>
       </c>
       <c r="BF221" s="41" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="BG221" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH221" s="41" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="BI221" s="56" t="s">
         <v>630</v>
@@ -68145,7 +68156,7 @@
         <v>636</v>
       </c>
       <c r="BF222" s="41" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="BG222" s="56" t="s">
         <v>636</v>
@@ -68272,13 +68283,13 @@
         <v>417</v>
       </c>
       <c r="BF225" s="41" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="BG225" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH225" s="41" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="BI225" s="56" t="s">
         <v>421</v>
@@ -68321,13 +68332,13 @@
         <v>455</v>
       </c>
       <c r="BF226" s="41" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="BG226" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH226" s="41" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="BI226" s="56" t="s">
         <v>458</v>
@@ -68370,13 +68381,13 @@
         <v>482</v>
       </c>
       <c r="BF227" s="41" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="BG227" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH227" s="41" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="BI227" s="56" t="s">
         <v>486</v>
@@ -68419,13 +68430,13 @@
         <v>519</v>
       </c>
       <c r="BF228" s="41" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="BG228" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH228" s="41" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="BI228" s="56" t="s">
         <v>523</v>
@@ -68468,13 +68479,13 @@
         <v>549</v>
       </c>
       <c r="BF229" s="41" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="BG229" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH229" s="41" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="BI229" s="56" t="s">
         <v>552</v>
@@ -68517,13 +68528,13 @@
         <v>576</v>
       </c>
       <c r="BF230" s="41" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="BG230" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH230" s="41" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="BI230" s="56" t="s">
         <v>579</v>
@@ -68566,13 +68577,13 @@
         <v>596</v>
       </c>
       <c r="BF231" s="41" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="BG231" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH231" s="41" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="BI231" s="56" t="s">
         <v>600</v>
@@ -68615,13 +68626,13 @@
         <v>627</v>
       </c>
       <c r="BF232" s="41" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="BG232" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH232" s="41" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="BI232" s="56" t="s">
         <v>630</v>
@@ -68664,7 +68675,7 @@
         <v>636</v>
       </c>
       <c r="BF233" s="41" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="BG233" s="56" t="s">
         <v>636</v>
@@ -68791,13 +68802,13 @@
         <v>417</v>
       </c>
       <c r="BF236" s="41" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="BG236" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH236" s="41" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="BI236" s="56" t="s">
         <v>421</v>
@@ -68840,13 +68851,13 @@
         <v>455</v>
       </c>
       <c r="BF237" s="41" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="BG237" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH237" s="41" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="BI237" s="56" t="s">
         <v>458</v>
@@ -68889,13 +68900,13 @@
         <v>482</v>
       </c>
       <c r="BF238" s="41" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="BG238" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH238" s="41" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="BI238" s="56" t="s">
         <v>486</v>
@@ -68938,13 +68949,13 @@
         <v>519</v>
       </c>
       <c r="BF239" s="41" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="BG239" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH239" s="41" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="BI239" s="56" t="s">
         <v>523</v>
@@ -68987,13 +68998,13 @@
         <v>549</v>
       </c>
       <c r="BF240" s="41" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="BG240" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH240" s="41" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="BI240" s="56" t="s">
         <v>552</v>
@@ -69036,13 +69047,13 @@
         <v>576</v>
       </c>
       <c r="BF241" s="41" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="BG241" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH241" s="41" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="BI241" s="56" t="s">
         <v>579</v>
@@ -69085,13 +69096,13 @@
         <v>596</v>
       </c>
       <c r="BF242" s="41" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="BG242" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH242" s="41" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="BI242" s="56" t="s">
         <v>600</v>
@@ -69134,13 +69145,13 @@
         <v>627</v>
       </c>
       <c r="BF243" s="41" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="BG243" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH243" s="41" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="BI243" s="56" t="s">
         <v>630</v>
@@ -69183,7 +69194,7 @@
         <v>636</v>
       </c>
       <c r="BF244" s="41" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="BG244" s="56" t="s">
         <v>636</v>
@@ -69653,7 +69664,7 @@
         <v>627</v>
       </c>
       <c r="BF254" s="41" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="BG254" s="56" t="s">
         <v>629</v>
@@ -69876,7 +69887,7 @@
         <v>455</v>
       </c>
       <c r="BF259" s="41" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="BG259" s="56" t="s">
         <v>456</v>
@@ -69968,7 +69979,7 @@
         <v>519</v>
       </c>
       <c r="BF261" s="41" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="BG261" s="56" t="s">
         <v>521</v>
@@ -70047,7 +70058,7 @@
         <v>576</v>
       </c>
       <c r="BF263" s="41" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="BG263" s="56" t="s">
         <v>578</v>
@@ -70084,7 +70095,7 @@
         <v>596</v>
       </c>
       <c r="BF264" s="41" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="BG264" s="56" t="s">
         <v>598</v>
@@ -70255,13 +70266,13 @@
         <v>417</v>
       </c>
       <c r="BF269" s="41" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="BG269" s="56" t="s">
         <v>419</v>
       </c>
       <c r="BH269" s="41" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="BI269" s="56" t="s">
         <v>421</v>
@@ -70294,13 +70305,13 @@
         <v>455</v>
       </c>
       <c r="BF270" s="41" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="BG270" s="56" t="s">
         <v>456</v>
       </c>
       <c r="BH270" s="41" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="BI270" s="56" t="s">
         <v>458</v>
@@ -70333,13 +70344,13 @@
         <v>482</v>
       </c>
       <c r="BF271" s="41" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="BG271" s="56" t="s">
         <v>484</v>
       </c>
       <c r="BH271" s="41" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="BI271" s="56" t="s">
         <v>486</v>
@@ -70372,13 +70383,13 @@
         <v>519</v>
       </c>
       <c r="BF272" s="41" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="BG272" s="56" t="s">
         <v>521</v>
       </c>
       <c r="BH272" s="41" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="BI272" s="56" t="s">
         <v>523</v>
@@ -70411,13 +70422,13 @@
         <v>549</v>
       </c>
       <c r="BF273" s="41" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="BG273" s="56" t="s">
         <v>551</v>
       </c>
       <c r="BH273" s="41" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="BI273" s="56" t="s">
         <v>552</v>
@@ -70450,13 +70461,13 @@
         <v>576</v>
       </c>
       <c r="BF274" s="41" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="BG274" s="56" t="s">
         <v>578</v>
       </c>
       <c r="BH274" s="41" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="BI274" s="56" t="s">
         <v>579</v>
@@ -70489,13 +70500,13 @@
         <v>596</v>
       </c>
       <c r="BF275" s="41" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="BG275" s="56" t="s">
         <v>598</v>
       </c>
       <c r="BH275" s="41" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="BI275" s="56" t="s">
         <v>600</v>
@@ -70528,13 +70539,13 @@
         <v>627</v>
       </c>
       <c r="BF276" s="41" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="BG276" s="56" t="s">
         <v>629</v>
       </c>
       <c r="BH276" s="41" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="BI276" s="56" t="s">
         <v>630</v>
@@ -70567,7 +70578,7 @@
         <v>636</v>
       </c>
       <c r="BF277" s="41" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="BG277" s="56" t="s">
         <v>636</v>
@@ -70760,7 +70771,7 @@
         <v>519</v>
       </c>
       <c r="BF283" s="41" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="BG283" s="56" t="s">
         <v>521</v>
@@ -70806,7 +70817,7 @@
         <v>576</v>
       </c>
       <c r="BF285" s="41" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="BG285" s="56" t="s">
         <v>578</v>
@@ -71463,46 +71474,46 @@
   <sheetData>
     <row r="1" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C1" s="81" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D1" s="81" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="H1" s="81" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="J1" s="81" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="K1" s="81" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="L1" s="81" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="M1" s="81" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="N1" s="81" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="AMI1" s="20"/>
       <c r="AMJ1" s="20"/>
@@ -71512,40 +71523,40 @@
         <v>417</v>
       </c>
       <c r="B2" s="82" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E2" s="83" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="F2" s="83" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="H2" s="83" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="I2" s="82" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="J2" s="82" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="K2" s="83" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="L2" s="83" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="M2" s="83" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="N2" s="83" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71553,40 +71564,40 @@
         <v>455</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E3" s="83" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="F3" s="83" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="G3" s="83" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="H3" s="83" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="I3" s="82" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="J3" s="82" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="K3" s="83" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="L3" s="83" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="M3" s="83" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="N3" s="83" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71594,40 +71605,40 @@
         <v>482</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E4" s="83" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="F4" s="83" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="G4" s="83" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="H4" s="83" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="I4" s="82" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="J4" s="82" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="K4" s="83" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="L4" s="83" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="N4" s="83" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71635,40 +71646,40 @@
         <v>519</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E5" s="83" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="F5" s="83" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="G5" s="83" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="H5" s="83" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="I5" s="82" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="J5" s="82" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="K5" s="83" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="L5" s="83" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="M5" s="83" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="N5" s="83" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71676,40 +71687,40 @@
         <v>549</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E6" s="83" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="F6" s="83" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="G6" s="83" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="H6" s="83" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="I6" s="82" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="J6" s="82" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="K6" s="83" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="L6" s="83" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="N6" s="83" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71717,40 +71728,40 @@
         <v>576</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="C7" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E7" s="83" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="F7" s="83" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="G7" s="83" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="H7" s="83" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="I7" s="82" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="J7" s="82" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="K7" s="83" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="L7" s="83" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="M7" s="83" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="N7" s="83" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71758,40 +71769,40 @@
         <v>596</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="C8" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="F8" s="83" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="G8" s="83" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="H8" s="83" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="I8" s="82" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="J8" s="82" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="K8" s="83" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="L8" s="83" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="M8" s="83" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="N8" s="83" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71799,40 +71810,40 @@
         <v>627</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E9" s="83" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="F9" s="83" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="G9" s="83" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="H9" s="83" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="I9" s="82" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="J9" s="82" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="K9" s="83" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="L9" s="83" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="M9" s="83" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="N9" s="83" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71840,202 +71851,202 @@
         <v>636</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="E10" s="83" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="F10" s="83" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="G10" s="83" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="H10" s="83" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="I10" s="82" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="J10" s="82" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="K10" s="83" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="L10" s="83" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="M10" s="83" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="N10" s="83" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="82" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="B12" s="82" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E12" s="83" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="F12" s="83" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="G12" s="83" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="H12" s="83" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="I12" s="82" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="J12" s="82" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="K12" s="83" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="L12" s="83" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="M12" s="83" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="N12" s="83" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="82" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="C13" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E13" s="83" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="F13" s="83" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="G13" s="83" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="H13" s="83" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="I13" s="82" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="J13" s="82" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="K13" s="83" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="L13" s="83" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="M13" s="83" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="N13" s="83" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="82" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="F14" s="83" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="G14" s="83" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="H14" s="83" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="I14" s="82" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="J14" s="82" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="K14" s="83" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="L14" s="83" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="M14" s="83" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="N14" s="83" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="82" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E15" s="83" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="F15" s="83" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="G15" s="83" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="H15" s="83" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="I15" s="82" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="J15" s="82" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="K15" s="83" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="L15" s="83" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="M15" s="83" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="N15" s="83" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -72044,40 +72055,40 @@
         <v>413</v>
       </c>
       <c r="B17" s="82" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="C17" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E17" s="83" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="F17" s="83" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="G17" s="83" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="H17" s="83" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="I17" s="82" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="J17" s="82" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="K17" s="83" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="L17" s="83" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="M17" s="83" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="N17" s="83" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -72085,40 +72096,40 @@
         <v>414</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="C18" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E18" s="83" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="F18" s="83" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="G18" s="83" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="H18" s="83" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="I18" s="82" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="J18" s="82" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="K18" s="83" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="L18" s="83" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="M18" s="83" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="N18" s="83" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -72129,597 +72140,597 @@
         <v>1300</v>
       </c>
       <c r="C19" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E19" s="83" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="F19" s="83" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="G19" s="83" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="H19" s="83" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="I19" s="82" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="J19" s="82" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="K19" s="83" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="L19" s="83" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="M19" s="83" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="N19" s="83" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="82" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="B21" s="82" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="C21" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E21" s="83" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="F21" s="83" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="G21" s="83" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="H21" s="83" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="I21" s="82" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="J21" s="82" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="K21" s="83" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="L21" s="83" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="M21" s="83" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="N21" s="83" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="82" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="C22" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E22" s="83" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="F22" s="83" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="G22" s="83" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="H22" s="83" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="I22" s="82" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="J22" s="82" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="K22" s="83" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="L22" s="83" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="M22" s="83" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="N22" s="83" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="82" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="B24" s="82" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="C24" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E24" s="83" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="F24" s="83" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="G24" s="83" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="H24" s="83" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="I24" s="82" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="J24" s="82" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="K24" s="83" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="L24" s="83" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="M24" s="83" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="N24" s="83" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="82" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="C25" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D25" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E25" s="83" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="F25" s="83" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="G25" s="83" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="H25" s="83" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="I25" s="82" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="J25" s="82" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="K25" s="83" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="L25" s="83" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="M25" s="83" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="N25" s="83" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="82" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="B26" s="82" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="C26" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D26" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E26" s="83" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="F26" s="83" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="G26" s="83" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="H26" s="83" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="I26" s="82" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="J26" s="82" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="K26" s="83" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="L26" s="83" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="M26" s="83" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="N26" s="83" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="82" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="B27" s="82" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="C27" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D27" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E27" s="83" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="F27" s="83" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="G27" s="83" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="H27" s="83" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="I27" s="82" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="J27" s="82" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="K27" s="83" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="L27" s="83" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="M27" s="83" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="N27" s="83" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="82" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="B28" s="82" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="C28" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D28" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E28" s="83" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="F28" s="83" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="G28" s="83" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="H28" s="83" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="I28" s="82" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="J28" s="82" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="K28" s="83" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="L28" s="83" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="M28" s="83" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="N28" s="83" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="82" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="B29" s="82" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="C29" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D29" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E29" s="83" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="F29" s="83" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="G29" s="83" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H29" s="83" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="I29" s="82" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="J29" s="82" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="K29" s="83" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="L29" s="83" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="M29" s="83" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="N29" s="83" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="82" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="B30" s="82" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="C30" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D30" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E30" s="83" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="F30" s="83" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="G30" s="83" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="H30" s="83" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="I30" s="82" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="J30" s="82" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="K30" s="83" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="L30" s="83" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="M30" s="83" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="N30" s="83" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="82" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="B31" s="82" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="C31" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D31" s="82" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E31" s="83" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="F31" s="83" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="G31" s="83" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="H31" s="83" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="I31" s="82" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="J31" s="82" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="K31" s="83" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="L31" s="83" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="M31" s="83" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="N31" s="83" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="82" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B33" s="82" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="C33" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E33" s="83" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="F33" s="83" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="G33" s="83" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="H33" s="83" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="I33" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="82" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="K33" s="83" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="L33" s="83" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="M33" s="83" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="N33" s="83" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="82" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="B34" s="82" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C34" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E34" s="83" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="F34" s="83" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="G34" s="83" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="H34" s="83" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="I34" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J34" s="82" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="K34" s="83" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="L34" s="83" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="M34" s="83" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="N34" s="83" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="82" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="B35" s="82" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C35" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E35" s="83" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="F35" s="83" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="G35" s="83" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="H35" s="83" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="I35" s="20" t="n">
         <v>3</v>
       </c>
       <c r="J35" s="82" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="K35" s="83" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="L35" s="83" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="M35" s="83" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="N35" s="83" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -72728,542 +72739,542 @@
         <v>32</v>
       </c>
       <c r="B37" s="82" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="C37" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G37" s="83" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="H37" s="83" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="I37" s="82" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="J37" s="82" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="M37" s="83" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="N37" s="83" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B38" s="82" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="C38" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E38" s="83" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="F38" s="83" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="G38" s="83" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="H38" s="83" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="I38" s="82" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="J38" s="82" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="K38" s="83" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="L38" s="83" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="M38" s="83" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="N38" s="83" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="82" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="B39" s="82" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="C39" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E39" s="83" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="F39" s="83" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="G39" s="83" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="H39" s="83" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="I39" s="82" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="J39" s="82" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="K39" s="83" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="L39" s="83" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="M39" s="83" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="N39" s="83" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C40" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="82" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B41" s="82" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C41" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E41" s="83" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="F41" s="83" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="G41" s="83" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="H41" s="83" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="I41" s="82" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="J41" s="82" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="K41" s="83" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="M41" s="83" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="N41" s="83" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="82" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="B42" s="82" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="C42" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E42" s="83" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="F42" s="83" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="G42" s="83" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="H42" s="83" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="I42" s="82" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="J42" s="82" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="K42" s="83" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="L42" s="83" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="M42" s="83" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="N42" s="83" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="82" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="B43" s="82" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="C43" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E43" s="83" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="F43" s="83" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="G43" s="83" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="H43" s="83" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="I43" s="82" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="J43" s="82" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="M43" s="83" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="N43" s="83" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="82" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="B44" s="82" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="C44" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E44" s="83" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="G44" s="83" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="H44" s="83" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="I44" s="82" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="J44" s="82" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="K44" s="83" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="L44" s="83" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="M44" s="83" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="N44" s="83" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="82" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="B45" s="82" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="C45" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E45" s="83" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="F45" s="83" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="G45" s="83" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="H45" s="83" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="I45" s="82" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="J45" s="82" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="K45" s="83" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="L45" s="83" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="M45" s="83" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="N45" s="83" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="82" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="B46" s="82" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C46" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E46" s="83" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="F46" s="83" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="G46" s="83" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="H46" s="83" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="I46" s="82" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="J46" s="82" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="K46" s="83" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="L46" s="83" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="M46" s="83" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="N46" s="83" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="82" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="C47" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E47" s="83" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="F47" s="83" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="G47" s="83" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="H47" s="83" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="I47" s="82" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="J47" s="82" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="K47" s="83" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="L47" s="83" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="M47" s="83" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="N47" s="83" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="82" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="B48" s="82" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C48" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E48" s="83" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="F48" s="83" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="G48" s="83" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="H48" s="83" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="I48" s="82" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="J48" s="82" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="K48" s="83" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="L48" s="83" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="M48" s="83" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="N48" s="83" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="82" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="B49" s="82" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="C49" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E49" s="83" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="F49" s="83" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="G49" s="83" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="H49" s="83" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="I49" s="82" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="J49" s="82" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="K49" s="83" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="L49" s="83" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="M49" s="83" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="N49" s="83" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="82" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="B50" s="82" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="C50" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G50" s="83" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="H50" s="83" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="I50" s="82" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="J50" s="82" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="M50" s="83" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="N50" s="83" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="82" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="B51" s="82" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="C51" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E51" s="83" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="F51" s="83" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="G51" s="83" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="H51" s="83" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="I51" s="82" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="J51" s="82" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="K51" s="83" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="L51" s="83" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="M51" s="83" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="N51" s="83" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -73274,498 +73285,498 @@
         <v>2</v>
       </c>
       <c r="C52" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E52" s="83" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="F52" s="83" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="G52" s="83" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="H52" s="83" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="I52" s="82" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="J52" s="82" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="K52" s="83" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="L52" s="83" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="M52" s="83" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="N52" s="83" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="82" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="B53" s="82" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="C53" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G53" s="83" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="H53" s="83" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="I53" s="82" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="J53" s="82" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="K53" s="83" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="L53" s="83" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="M53" s="83" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="N53" s="83" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="82" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="B54" s="82" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="C54" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E54" s="83" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="F54" s="83" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="G54" s="83" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="H54" s="83" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="I54" s="82" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="J54" s="82" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="K54" s="83" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="L54" s="83" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="M54" s="83" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="N54" s="83" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="82" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="B55" s="82" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="C55" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E55" s="83" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="F55" s="83" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="G55" s="83" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="H55" s="83" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="I55" s="82" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="J55" s="82" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="K55" s="83" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="L55" s="83" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="M55" s="83" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="N55" s="83" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="82" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="B56" s="82" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="C56" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E56" s="83" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="F56" s="83" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="G56" s="83" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="H56" s="83" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="I56" s="82" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="J56" s="82" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="K56" s="83" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="L56" s="83" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="M56" s="83" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="N56" s="83" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="82" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="B57" s="82" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="C57" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E57" s="83" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="F57" s="83" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="G57" s="83" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="H57" s="83" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="I57" s="82" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="J57" s="82" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="K57" s="83" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="L57" s="83" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="M57" s="83" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="N57" s="83" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="82" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="B58" s="82" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="C58" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E58" s="83" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="F58" s="83" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="G58" s="83" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="H58" s="83" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="I58" s="82" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="J58" s="82" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="K58" s="83" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="L58" s="83" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="M58" s="83" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="N58" s="83" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="82" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="B59" s="82" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="C59" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G59" s="83" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="H59" s="83" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="I59" s="82" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="J59" s="82" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="K59" s="83" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="L59" s="83" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="M59" s="83" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="N59" s="83" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="82" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="B60" s="82" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="C60" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E60" s="83" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="F60" s="83" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="G60" s="83" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="H60" s="83" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="I60" s="82" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="J60" s="82" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="K60" s="83" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="L60" s="83" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="M60" s="83" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="N60" s="83" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="82" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="B61" s="82" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="C61" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E61" s="83" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="F61" s="83" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="G61" s="83" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="H61" s="83" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="I61" s="82" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="J61" s="82" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="K61" s="83" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="L61" s="83" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="M61" s="83" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="N61" s="83" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="82" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="B62" s="82" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="C62" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E62" s="83" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="F62" s="83" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="G62" s="83" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="H62" s="83" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="I62" s="82" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="J62" s="82" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="K62" s="83" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="L62" s="83" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="M62" s="83" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="N62" s="83" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="82" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="B63" s="82" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="C63" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="E63" s="83" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="F63" s="83" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="G63" s="83" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="H63" s="83" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="I63" s="82" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="J63" s="82" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="K63" s="83" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="L63" s="83" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="M63" s="83" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="N63" s="83" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="82" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="B64" s="82" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="C64" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="82" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="B66" s="82" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="C66" s="82" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
   </sheetData>
@@ -73793,174 +73804,174 @@
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2"/>
       <c r="B1" s="84" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="C1" s="84" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="84" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B2" s="84" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C2" s="84" t="s">
         <v>2650</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>2649</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="84" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="84" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="84" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="C5" s="84" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="84" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="84" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="B7" s="84" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="84" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="B8" s="84" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="84" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="84" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="B10" s="84" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="84" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="B11" s="84" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="84" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="B12" s="84" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="C12" s="84" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="84" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="84" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="B14" s="84" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="84" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B15" s="84" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="C15" s="84" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="84" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B16" s="84" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="84" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="B17" s="84" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="84" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="B18" s="84" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="C18" s="2"/>
     </row>

--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -3310,7 +3310,28 @@
     <t xml:space="preserve">catunnaṃ</t>
   </si>
   <si>
-    <t xml:space="preserve">catassannaṃ</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Crimson Pro"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">catassannaṃ
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Crimson Pro"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">catunnaṃ</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">assa
@@ -9182,7 +9203,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -9271,6 +9292,13 @@
       <name val="Crimson Pro"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Crimson Pro"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -9783,11 +9811,11 @@
       <alignment horizontal="justify" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9795,11 +9823,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9823,7 +9851,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
